--- a/entregables_varones/METRADO_DRENAJE_PLUVIAL_CAR_VARONES_CON_COLECTOR.xlsx
+++ b/entregables_varones/METRADO_DRENAJE_PLUVIAL_CAR_VARONES_CON_COLECTOR.xlsx
@@ -4461,7 +4461,7 @@
       </c>
       <c r="B80" s="160" t="inlineStr">
         <is>
-          <t>JUNTA DE TECNOPOR E=1" ENTRE COLECTOR, CERCO, PISO ADYACENTE Y CAJA CL</t>
+          <t>JUNTA DE TECNOPOR E=1" ENTRE COLECTOR, PISO ADYACENTE Y CAJA CL</t>
         </is>
       </c>
       <c r="C80" s="161" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C16" s="184" t="n"/>
       <c r="D16" s="190" t="n">
-        <v>102.58</v>
+        <v>102.31</v>
       </c>
       <c r="E16" s="188">
         <f>+'CONCRETO EN CUNETAS'!E46</f>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="C18" s="184" t="n"/>
       <c r="D18" s="190" t="n">
-        <v>98.70999999999999</v>
+        <v>98.69</v>
       </c>
       <c r="E18" s="188">
         <f>+'CONCRETO EN CUNETAS'!E70</f>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="C20" s="184" t="n"/>
       <c r="D20" s="190" t="n">
-        <v>60.61</v>
+        <v>60.6</v>
       </c>
       <c r="E20" s="188">
         <f>+'CONCRETO EN CUNETAS'!M22</f>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="C21" s="184" t="n"/>
       <c r="D21" s="190" t="n">
-        <v>42.46</v>
+        <v>42.45</v>
       </c>
       <c r="E21" s="188">
         <f>+'CONCRETO EN CUNETAS'!M34</f>
@@ -5935,7 +5935,7 @@
         <v>105.7</v>
       </c>
       <c r="D11" s="368" t="n">
-        <v>3.12</v>
+        <v>3.39</v>
       </c>
       <c r="E11" s="369">
         <f>C11-D11</f>
@@ -5965,7 +5965,7 @@
         <v>98.95</v>
       </c>
       <c r="D12" s="368" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="E12" s="369">
         <f>C12-D12</f>
@@ -5995,7 +5995,7 @@
         <v>60.7</v>
       </c>
       <c r="D13" s="368" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="E13" s="369">
         <f>C13-D13</f>
@@ -6025,7 +6025,7 @@
         <v>42.7</v>
       </c>
       <c r="D14" s="368" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="E14" s="369">
         <f>C14-D14</f>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="B47" s="378" t="inlineStr">
         <is>
-          <t>Progresiva del quiebre (fin del tramo pegado al cerco)</t>
+          <t>Progresiva del quiebre (inicio del tramo de empalme)</t>
         </is>
       </c>
       <c r="C47" s="379" t="n">
@@ -11107,7 +11107,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>102.58</v>
+        <v>102.31</v>
       </c>
       <c r="E15" s="31" t="n">
         <v>1.4</v>
@@ -11161,7 +11161,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="31" t="n">
-        <v>98.70999999999999</v>
+        <v>98.69</v>
       </c>
       <c r="E17" s="31" t="n">
         <v>1.4</v>
@@ -11215,7 +11215,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="31" t="n">
-        <v>60.61</v>
+        <v>60.6</v>
       </c>
       <c r="E19" s="31" t="n">
         <v>1.4</v>
@@ -11242,7 +11242,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="31" t="n">
-        <v>42.46</v>
+        <v>42.45</v>
       </c>
       <c r="E20" s="31" t="n">
         <v>1.4</v>
@@ -11436,7 +11436,7 @@
         <v>1</v>
       </c>
       <c r="D28" s="31" t="n">
-        <v>102.58</v>
+        <v>102.31</v>
       </c>
       <c r="E28" s="31" t="n">
         <v>1.4</v>
@@ -11490,7 +11490,7 @@
         <v>1</v>
       </c>
       <c r="D30" s="31" t="n">
-        <v>98.70999999999999</v>
+        <v>98.69</v>
       </c>
       <c r="E30" s="31" t="n">
         <v>1.4</v>
@@ -11544,7 +11544,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="31" t="n">
-        <v>60.61</v>
+        <v>60.6</v>
       </c>
       <c r="E32" s="31" t="n">
         <v>1.4</v>
@@ -11571,7 +11571,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="31" t="n">
-        <v>42.46</v>
+        <v>42.45</v>
       </c>
       <c r="E33" s="31" t="n">
         <v>1.4</v>
@@ -11793,7 +11793,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="31" t="n">
-        <v>102.58</v>
+        <v>102.31</v>
       </c>
       <c r="E42" s="31" t="n">
         <v>1.4</v>
@@ -11851,7 +11851,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="31" t="n">
-        <v>98.70999999999999</v>
+        <v>98.69</v>
       </c>
       <c r="E44" s="31" t="n">
         <v>1.4</v>
@@ -11909,7 +11909,7 @@
         <v>1</v>
       </c>
       <c r="D46" s="31" t="n">
-        <v>60.61</v>
+        <v>60.6</v>
       </c>
       <c r="E46" s="31" t="n">
         <v>1.4</v>
@@ -11938,7 +11938,7 @@
         <v>1</v>
       </c>
       <c r="D47" s="31" t="n">
-        <v>42.46</v>
+        <v>42.45</v>
       </c>
       <c r="E47" s="31" t="n">
         <v>1.4</v>
@@ -12206,7 +12206,7 @@
         <v>1</v>
       </c>
       <c r="D58" s="31" t="n">
-        <v>102.58</v>
+        <v>102.31</v>
       </c>
       <c r="E58" s="31" t="n">
         <v>0.6</v>
@@ -12260,7 +12260,7 @@
         <v>1</v>
       </c>
       <c r="D60" s="31" t="n">
-        <v>98.70999999999999</v>
+        <v>98.69</v>
       </c>
       <c r="E60" s="31" t="n">
         <v>0.6</v>
@@ -12314,7 +12314,7 @@
         <v>1</v>
       </c>
       <c r="D62" s="31" t="n">
-        <v>60.61</v>
+        <v>60.6</v>
       </c>
       <c r="E62" s="31" t="n">
         <v>0.6</v>
@@ -12341,7 +12341,7 @@
         <v>1</v>
       </c>
       <c r="D63" s="31" t="n">
-        <v>42.46</v>
+        <v>42.45</v>
       </c>
       <c r="E63" s="31" t="n">
         <v>0.6</v>
@@ -12541,7 +12541,7 @@
         <v>1</v>
       </c>
       <c r="D71" s="31" t="n">
-        <v>102.58</v>
+        <v>102.31</v>
       </c>
       <c r="E71" s="31" t="n">
         <v>0.8</v>
@@ -12599,7 +12599,7 @@
         <v>1</v>
       </c>
       <c r="D73" s="31" t="n">
-        <v>98.70999999999999</v>
+        <v>98.69</v>
       </c>
       <c r="E73" s="31" t="n">
         <v>0.8</v>
@@ -12657,7 +12657,7 @@
         <v>1</v>
       </c>
       <c r="D75" s="31" t="n">
-        <v>60.61</v>
+        <v>60.6</v>
       </c>
       <c r="E75" s="31" t="n">
         <v>0.8</v>
@@ -12686,7 +12686,7 @@
         <v>1</v>
       </c>
       <c r="D76" s="31" t="n">
-        <v>42.46</v>
+        <v>42.45</v>
       </c>
       <c r="E76" s="31" t="n">
         <v>0.8</v>
@@ -12988,7 +12988,7 @@
         <v>1</v>
       </c>
       <c r="D88" s="31" t="n">
-        <v>102.58</v>
+        <v>102.31</v>
       </c>
       <c r="E88" s="31" t="n">
         <v>0.6</v>
@@ -13042,7 +13042,7 @@
         <v>1</v>
       </c>
       <c r="D90" s="31" t="n">
-        <v>98.70999999999999</v>
+        <v>98.69</v>
       </c>
       <c r="E90" s="31" t="n">
         <v>0.6</v>
@@ -13096,7 +13096,7 @@
         <v>1</v>
       </c>
       <c r="D92" s="31" t="n">
-        <v>60.61</v>
+        <v>60.6</v>
       </c>
       <c r="E92" s="31" t="n">
         <v>0.6</v>
@@ -13123,7 +13123,7 @@
         <v>1</v>
       </c>
       <c r="D93" s="31" t="n">
-        <v>42.46</v>
+        <v>42.45</v>
       </c>
       <c r="E93" s="31" t="n">
         <v>0.6</v>
@@ -16604,7 +16604,7 @@
       </c>
       <c r="B237" s="28" t="inlineStr">
         <is>
-          <t>JUNTA DE TECNOPOR E=1" ENTRE COLECTOR, CERCO, PISO ADYACENTE Y CAJA CL</t>
+          <t>JUNTA DE TECNOPOR E=1" ENTRE COLECTOR, PISO ADYACENTE Y CAJA CL</t>
         </is>
       </c>
       <c r="C237" s="29" t="n"/>
@@ -16616,7 +16616,7 @@
       <c r="I237" s="29" t="n"/>
       <c r="J237" s="29" t="n"/>
       <c r="K237" s="29">
-        <f>+'COLECTOR JUNTAS Y EMPALMES'!F19</f>
+        <f>+'COLECTOR JUNTAS Y EMPALMES'!F17</f>
         <v/>
       </c>
       <c r="L237" s="28" t="inlineStr">
@@ -16645,7 +16645,7 @@
       <c r="I238" s="29" t="n"/>
       <c r="J238" s="29" t="n"/>
       <c r="K238" s="29">
-        <f>+'COLECTOR JUNTAS Y EMPALMES'!F26</f>
+        <f>+'COLECTOR JUNTAS Y EMPALMES'!F24</f>
         <v/>
       </c>
       <c r="L238" s="28" t="inlineStr">
@@ -16818,7 +16818,7 @@
       </c>
       <c r="C10" s="377" t="inlineStr">
         <is>
-          <t>0+006.24</t>
+          <t>0+006.30</t>
         </is>
       </c>
       <c r="D10" s="378" t="inlineStr">
@@ -16846,7 +16846,7 @@
       </c>
       <c r="C11" s="377" t="inlineStr">
         <is>
-          <t>0+013.05</t>
+          <t>0+013.16</t>
         </is>
       </c>
       <c r="D11" s="378" t="inlineStr">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C12" s="377" t="inlineStr">
         <is>
-          <t>0+019.87</t>
+          <t>0+020.02</t>
         </is>
       </c>
       <c r="D12" s="378" t="inlineStr">
@@ -16902,7 +16902,7 @@
       </c>
       <c r="C13" s="377" t="inlineStr">
         <is>
-          <t>0+028.59</t>
+          <t>0+028.72</t>
         </is>
       </c>
       <c r="D13" s="378" t="inlineStr">
@@ -16930,7 +16930,7 @@
       </c>
       <c r="C14" s="377" t="inlineStr">
         <is>
-          <t>0+037.30</t>
+          <t>0+037.41</t>
         </is>
       </c>
       <c r="D14" s="378" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="C15" s="377" t="inlineStr">
         <is>
-          <t>0+046.02</t>
+          <t>0+046.11</t>
         </is>
       </c>
       <c r="D15" s="378" t="inlineStr">
@@ -16986,7 +16986,7 @@
       </c>
       <c r="C16" s="377" t="inlineStr">
         <is>
-          <t>0+056.79</t>
+          <t>0+056.47</t>
         </is>
       </c>
       <c r="D16" s="378" t="inlineStr">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="C17" s="377" t="inlineStr">
         <is>
-          <t>0+067.56</t>
+          <t>0+066.84</t>
         </is>
       </c>
       <c r="D17" s="378" t="inlineStr">
@@ -17042,7 +17042,7 @@
       </c>
       <c r="C18" s="377" t="inlineStr">
         <is>
-          <t>0+078.33</t>
+          <t>0+077.20</t>
         </is>
       </c>
       <c r="D18" s="378" t="inlineStr">
@@ -17070,7 +17070,7 @@
       </c>
       <c r="C19" s="377" t="inlineStr">
         <is>
-          <t>0+089.61</t>
+          <t>0+089.05</t>
         </is>
       </c>
       <c r="D19" s="378" t="inlineStr">
@@ -17372,7 +17372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -17464,7 +17464,7 @@
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="365" t="inlineStr">
         <is>
-          <t>Laminas DP-01, DP-02, DP-06C, DP-07 y DD-03. Junta de dilatacion de 1" cada 4.00 m en todo el perimetro de la seccion (tecnopor + sellador elastomerico). Junta de tecnopor de 1" entre el colector y el cimiento del cerco, en el paso del cerco proyectado, entre el borde de la losa y el piso adyacente y en el contacto con la caja CL. Empalme de cada cuneta por ventana en el muro lado predio con caida libre al fondo (sin dintel adicional).</t>
+          <t>Laminas DP-01, DP-02, DP-06C, DP-07 y DD-03. Junta de dilatacion de 1" cada 4.00 m en todo el perimetro de la seccion (tecnopor + sellador elastomerico). Junta de tecnopor de 1" entre el borde de la losa y el piso adyacente (no hay cerco perimetrico) y en el contacto con la caja CL. Empalme de cada cuneta por ventana en el muro lado predio con caida libre al fondo (sin dintel adicional).</t>
         </is>
       </c>
       <c r="B7" s="362" t="n"/>
@@ -17577,7 +17577,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="388" t="inlineStr">
         <is>
-          <t>JUNTA DE TECNOPOR e=1" ENTRE COLECTOR, CERCO, PISO ADYACENTE Y CAJA CL</t>
+          <t>JUNTA DE TECNOPOR e=1" ENTRE COLECTOR, PISO ADYACENTE Y CAJA CL (el frente de Varones no tiene cerco perimetrico)</t>
         </is>
       </c>
       <c r="B14" s="395" t="n"/>
@@ -17593,18 +17593,18 @@
       </c>
       <c r="B15" s="378" t="inlineStr">
         <is>
-          <t>Contra el cimiento del cerco (tramo pegado al cerco, 0+000 al quiebre)</t>
+          <t>Borde de la losa con el piso adyacente: colector (ambos lados)</t>
         </is>
       </c>
       <c r="C15" s="396">
-        <f>"0+000.00 a 0+"&amp;TEXT('COLECTOR PARAMETROS'!$C$47,"000.00")</f>
+        <f>"2 x 0+"&amp;TEXT('COLECTOR PARAMETROS'!$C$46,"000.00")</f>
         <v/>
       </c>
       <c r="D15" s="393" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="384">
-        <f>'COLECTOR PARAMETROS'!$C$47</f>
+        <f>'COLECTOR PARAMETROS'!$C$46</f>
         <v/>
       </c>
       <c r="F15" s="384">
@@ -17613,7 +17613,7 @@
       </c>
       <c r="G15" s="370" t="inlineStr">
         <is>
-          <t>DP-01, DP-04 (junta entre muro y cimiento del cerco)</t>
+          <t>DP-04, DD-03: junta de tecnopor en el borde de la losa superior</t>
         </is>
       </c>
     </row>
@@ -17623,19 +17623,19 @@
       </c>
       <c r="B16" s="378" t="inlineStr">
         <is>
-          <t>Paso del cerco proyectado en el tramo de empalme (ambas caras del colector, altura del cajon)</t>
+          <t>Contacto del colector con el muro este de la caja CL (perimetro de la seccion)</t>
         </is>
       </c>
       <c r="C16" s="377" t="inlineStr">
         <is>
-          <t>0+102.11</t>
+          <t>0+105.29</t>
         </is>
       </c>
       <c r="D16" s="393" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="384">
-        <f>'COLECTOR PARAMETROS'!$C$12+'COLECTOR PARAMETROS'!$C$45+'COLECTOR PARAMETROS'!$C$13</f>
+        <f>2*('COLECTOR PARAMETROS'!$C$10+2*'COLECTOR PARAMETROS'!$C$11)+2*('COLECTOR PARAMETROS'!$C$12+'COLECTOR PARAMETROS'!$C$45+'COLECTOR PARAMETROS'!$C$13)</f>
         <v/>
       </c>
       <c r="F16" s="384">
@@ -17644,115 +17644,110 @@
       </c>
       <c r="G16" s="370" t="inlineStr">
         <is>
-          <t>DP-01, DP-07: paso de 0.95 m con tecnopor a ambos lados</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="377" t="n">
-        <v>3</v>
-      </c>
-      <c r="B17" s="378" t="inlineStr">
-        <is>
-          <t>Borde de la losa con el piso adyacente: colector (ambos lados)</t>
-        </is>
-      </c>
-      <c r="C17" s="396">
-        <f>"2 x 0+"&amp;TEXT('COLECTOR PARAMETROS'!$C$46,"000.00")</f>
-        <v/>
-      </c>
-      <c r="D17" s="393" t="n">
+          <t>DP-07: tecnopor en todo el contacto colector - CL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="385" t="inlineStr">
+        <is>
+          <t>TOTAL JUNTA DE TECNOPOR (m)</t>
+        </is>
+      </c>
+      <c r="B17" s="397" t="n"/>
+      <c r="C17" s="386" t="n"/>
+      <c r="D17" s="386" t="n"/>
+      <c r="E17" s="386" t="n"/>
+      <c r="F17" s="387">
+        <f>SUM(F15:F16)</f>
+        <v/>
+      </c>
+      <c r="G17" s="386" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="398" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="388" t="inlineStr">
+        <is>
+          <t>EMPALME DE CUNETA AL COLECTOR (ventana 0.40 x H en el muro lado predio, caida libre y registro encima) - laminas DP-06C y DD-04</t>
+        </is>
+      </c>
+      <c r="B19" s="395" t="n"/>
+      <c r="C19" s="389" t="n"/>
+      <c r="D19" s="389" t="n"/>
+      <c r="E19" s="389" t="n"/>
+      <c r="F19" s="389" t="n"/>
+      <c r="G19" s="389" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="377" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="378" t="inlineStr">
+        <is>
+          <t>Cuneta Eje 09 (registro RV-01)</t>
+        </is>
+      </c>
+      <c r="C20" s="377" t="inlineStr">
+        <is>
+          <t>0+006.30</t>
+        </is>
+      </c>
+      <c r="D20" s="393" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="362" t="n"/>
+      <c r="F20" s="392">
+        <f>D20</f>
+        <v/>
+      </c>
+      <c r="G20" s="370" t="inlineStr">
+        <is>
+          <t>DP-06C (cuadro de empalmes); DP-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="377" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="384">
-        <f>'COLECTOR PARAMETROS'!$C$46</f>
-        <v/>
-      </c>
-      <c r="F17" s="384">
-        <f>D17*E17</f>
-        <v/>
-      </c>
-      <c r="G17" s="370" t="inlineStr">
-        <is>
-          <t>DP-04: junta de tecnopor en el borde de la losa superior</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="377" t="n">
-        <v>4</v>
-      </c>
-      <c r="B18" s="378" t="inlineStr">
-        <is>
-          <t>Contacto del colector con el muro este de la caja CL (perimetro de la seccion)</t>
-        </is>
-      </c>
-      <c r="C18" s="377" t="inlineStr">
-        <is>
-          <t>0+105.29</t>
-        </is>
-      </c>
-      <c r="D18" s="393" t="n">
+      <c r="B21" s="378" t="inlineStr">
+        <is>
+          <t>Cuneta Eje 08 (registro RV-03)</t>
+        </is>
+      </c>
+      <c r="C21" s="377" t="inlineStr">
+        <is>
+          <t>0+020.02</t>
+        </is>
+      </c>
+      <c r="D21" s="393" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="384">
-        <f>2*('COLECTOR PARAMETROS'!$C$10+2*'COLECTOR PARAMETROS'!$C$11)+2*('COLECTOR PARAMETROS'!$C$12+'COLECTOR PARAMETROS'!$C$45+'COLECTOR PARAMETROS'!$C$13)</f>
-        <v/>
-      </c>
-      <c r="F18" s="384">
-        <f>D18*E18</f>
-        <v/>
-      </c>
-      <c r="G18" s="370" t="inlineStr">
-        <is>
-          <t>DP-07: tecnopor en todo el contacto colector - CL</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="385" t="inlineStr">
-        <is>
-          <t>TOTAL JUNTA DE TECNOPOR (m)</t>
-        </is>
-      </c>
-      <c r="B19" s="397" t="n"/>
-      <c r="C19" s="386" t="n"/>
-      <c r="D19" s="386" t="n"/>
-      <c r="E19" s="386" t="n"/>
-      <c r="F19" s="387">
-        <f>SUM(F15:F18)</f>
-        <v/>
-      </c>
-      <c r="G19" s="386" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="398" t="n"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="388" t="inlineStr">
-        <is>
-          <t>EMPALME DE CUNETA AL COLECTOR (ventana 0.40 x H en el muro lado predio, caida libre y registro encima) - laminas DP-06C y DD-04</t>
-        </is>
-      </c>
-      <c r="B21" s="395" t="n"/>
-      <c r="C21" s="389" t="n"/>
-      <c r="D21" s="389" t="n"/>
-      <c r="E21" s="389" t="n"/>
-      <c r="F21" s="389" t="n"/>
-      <c r="G21" s="389" t="n"/>
+      <c r="E21" s="362" t="n"/>
+      <c r="F21" s="392">
+        <f>D21</f>
+        <v/>
+      </c>
+      <c r="G21" s="370" t="inlineStr">
+        <is>
+          <t>DP-06C (cuadro de empalmes); DP-01</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="377" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B22" s="378" t="inlineStr">
         <is>
-          <t>Cuneta Eje 09 (registro RV-01)</t>
+          <t>Cuneta Eje 06 (registro RV-06)</t>
         </is>
       </c>
       <c r="C22" s="377" t="inlineStr">
         <is>
-          <t>0+006.24</t>
+          <t>0+046.11</t>
         </is>
       </c>
       <c r="D22" s="393" t="n">
@@ -17771,16 +17766,16 @@
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="377" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B23" s="378" t="inlineStr">
         <is>
-          <t>Cuneta Eje 08 (registro RV-03)</t>
+          <t>Cuneta Eje 04 (registro RV-09)</t>
         </is>
       </c>
       <c r="C23" s="377" t="inlineStr">
         <is>
-          <t>0+019.87</t>
+          <t>0+077.20</t>
         </is>
       </c>
       <c r="D23" s="393" t="n">
@@ -17797,80 +17792,24 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="377" t="n">
-        <v>3</v>
-      </c>
-      <c r="B24" s="378" t="inlineStr">
-        <is>
-          <t>Cuneta Eje 06 (registro RV-06)</t>
-        </is>
-      </c>
-      <c r="C24" s="377" t="inlineStr">
-        <is>
-          <t>0+046.02</t>
-        </is>
-      </c>
-      <c r="D24" s="393" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="362" t="n"/>
-      <c r="F24" s="392">
-        <f>D24</f>
-        <v/>
-      </c>
-      <c r="G24" s="370" t="inlineStr">
-        <is>
-          <t>DP-06C (cuadro de empalmes); DP-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="377" t="n">
-        <v>4</v>
-      </c>
-      <c r="B25" s="378" t="inlineStr">
-        <is>
-          <t>Cuneta Eje 04 (registro RV-09)</t>
-        </is>
-      </c>
-      <c r="C25" s="377" t="inlineStr">
-        <is>
-          <t>0+078.33</t>
-        </is>
-      </c>
-      <c r="D25" s="393" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="362" t="n"/>
-      <c r="F25" s="392">
-        <f>D25</f>
-        <v/>
-      </c>
-      <c r="G25" s="370" t="inlineStr">
-        <is>
-          <t>DP-06C (cuadro de empalmes); DP-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="385" t="inlineStr">
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="385" t="inlineStr">
         <is>
           <t>TOTAL EMPALMES (und)</t>
         </is>
       </c>
-      <c r="B26" s="397" t="n"/>
-      <c r="C26" s="386" t="n"/>
-      <c r="D26" s="386" t="n"/>
-      <c r="E26" s="386" t="n"/>
-      <c r="F26" s="394">
-        <f>SUM(F22:F25)</f>
-        <v/>
-      </c>
-      <c r="G26" s="386" t="n"/>
-    </row>
-    <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="371" t="inlineStr">
+      <c r="B24" s="397" t="n"/>
+      <c r="C24" s="386" t="n"/>
+      <c r="D24" s="386" t="n"/>
+      <c r="E24" s="386" t="n"/>
+      <c r="F24" s="394">
+        <f>SUM(F20:F23)</f>
+        <v/>
+      </c>
+      <c r="G24" s="386" t="n"/>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="371" t="inlineStr">
         <is>
           <t>Nota: la cuneta del Eje 01 no entra al colector: cae directamente a la caja CL por una ventana en su muro norte (DP-07); esa ventana y la del muro este (llegada del colector) se dejan en la caja CL del expediente del Hogar de Refugio. Las cunetas se acortan hasta el muro (hoja CUNETAS - LLEGADA AL COLECTOR).</t>
         </is>
@@ -17884,11 +17823,11 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A21:G21"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A26:G26"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="C3:G3"/>
@@ -20423,7 +20362,7 @@
         </is>
       </c>
       <c r="M26" s="14" t="n">
-        <v>60.61</v>
+        <v>60.6</v>
       </c>
       <c r="N26" s="325" t="n"/>
       <c r="O26" s="325" t="n"/>
@@ -20486,7 +20425,7 @@
         </is>
       </c>
       <c r="M28" s="14" t="n">
-        <v>10.76</v>
+        <v>10.75</v>
       </c>
       <c r="N28" s="322">
         <f>M28*M29*M30</f>
@@ -20636,7 +20575,7 @@
         </is>
       </c>
       <c r="M34" s="80" t="n">
-        <v>17.56</v>
+        <v>17.55</v>
       </c>
       <c r="N34" s="319">
         <f>M34*M35*M36</f>
@@ -20760,7 +20699,7 @@
         </is>
       </c>
       <c r="M38" s="14" t="n">
-        <v>42.46</v>
+        <v>42.45</v>
       </c>
       <c r="N38" s="325" t="n"/>
       <c r="O38" s="326" t="n"/>
@@ -20823,7 +20762,7 @@
         </is>
       </c>
       <c r="M40" s="80" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
       <c r="N40" s="319">
         <f>M40*M41*M42</f>
@@ -20946,7 +20885,7 @@
         </is>
       </c>
       <c r="E46" s="80" t="n">
-        <v>54.48</v>
+        <v>54.29</v>
       </c>
       <c r="F46" s="319">
         <f>E46*E47*E48</f>
@@ -21080,7 +21019,7 @@
         </is>
       </c>
       <c r="E50" s="14" t="n">
-        <v>102.58</v>
+        <v>102.31</v>
       </c>
       <c r="F50" s="325" t="n"/>
       <c r="G50" s="326" t="n"/>
@@ -21136,7 +21075,7 @@
         </is>
       </c>
       <c r="E52" s="172" t="n">
-        <v>30.93</v>
+        <v>30.66</v>
       </c>
       <c r="F52" s="218">
         <f>E52*E53*E54</f>
@@ -21613,7 +21552,7 @@
         </is>
       </c>
       <c r="E70" s="80" t="n">
-        <v>52.72</v>
+        <v>52.71</v>
       </c>
       <c r="F70" s="319">
         <f>E70*E71*E72</f>
@@ -21747,7 +21686,7 @@
         </is>
       </c>
       <c r="E74" s="14" t="n">
-        <v>98.70999999999999</v>
+        <v>98.69</v>
       </c>
       <c r="F74" s="325" t="n"/>
       <c r="G74" s="326" t="n"/>
@@ -21803,7 +21742,7 @@
         </is>
       </c>
       <c r="E76" s="80" t="n">
-        <v>66.20999999999999</v>
+        <v>66.19</v>
       </c>
       <c r="F76" s="319">
         <f>E76*E77*E78</f>
@@ -22884,7 +22823,7 @@
         </is>
       </c>
       <c r="N27" s="85" t="n">
-        <v>24.95</v>
+        <v>24.7</v>
       </c>
       <c r="O27" s="251">
         <f>N27*N28</f>
@@ -22956,7 +22895,7 @@
         </is>
       </c>
       <c r="N29" s="85" t="n">
-        <v>18.76</v>
+        <v>18.57</v>
       </c>
       <c r="O29" s="251">
         <f>N29*N30+N31</f>
@@ -23017,7 +22956,7 @@
         </is>
       </c>
       <c r="N31" s="85">
-        <f>30.93*0.4</f>
+        <f>30.66*0.4</f>
         <v/>
       </c>
       <c r="O31" s="315" t="n"/>
@@ -23285,7 +23224,7 @@
         </is>
       </c>
       <c r="N38" s="14" t="n">
-        <v>53.6</v>
+        <v>53.59</v>
       </c>
       <c r="O38" s="251">
         <f>N38*N39</f>
@@ -23357,7 +23296,7 @@
         </is>
       </c>
       <c r="N40" s="14" t="n">
-        <v>40.36</v>
+        <v>40.35</v>
       </c>
       <c r="O40" s="251">
         <f>N40*N41+N42</f>
@@ -23419,7 +23358,7 @@
         </is>
       </c>
       <c r="N42" s="14">
-        <f>66.21*0.4</f>
+        <f>66.19*0.4</f>
         <v/>
       </c>
       <c r="O42" s="315" t="n"/>
@@ -23687,7 +23626,7 @@
         </is>
       </c>
       <c r="N49" s="14" t="n">
-        <v>8.33</v>
+        <v>8.32</v>
       </c>
       <c r="O49" s="251">
         <f>N49*N50</f>
@@ -23820,7 +23759,7 @@
         </is>
       </c>
       <c r="N53" s="14">
-        <f>10.76*0.4</f>
+        <f>10.75*0.4</f>
         <v/>
       </c>
       <c r="O53" s="315" t="n"/>
@@ -24062,7 +24001,7 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>4.76</v>
+        <v>4.75</v>
       </c>
       <c r="G61" s="251">
         <f>F61*F62</f>
@@ -24136,7 +24075,7 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="G63" s="251">
         <f>F63*F64+F65</f>
@@ -24202,7 +24141,7 @@
         </is>
       </c>
       <c r="F65" s="14">
-        <f>6.46*0.4</f>
+        <f>6.45*0.4</f>
         <v/>
       </c>
       <c r="G65" s="315" t="n"/>
@@ -28650,7 +28589,7 @@
         </is>
       </c>
       <c r="G18" s="107" t="n">
-        <v>25.43</v>
+        <v>25.16</v>
       </c>
       <c r="H18" s="106" t="inlineStr">
         <is>
@@ -29142,7 +29081,7 @@
         </is>
       </c>
       <c r="G22" s="107" t="n">
-        <v>66.20999999999999</v>
+        <v>66.19</v>
       </c>
       <c r="H22" s="106" t="inlineStr">
         <is>
@@ -29505,7 +29444,7 @@
         </is>
       </c>
       <c r="G25" s="107" t="n">
-        <v>10.76</v>
+        <v>10.75</v>
       </c>
       <c r="H25" s="106" t="inlineStr">
         <is>
@@ -29751,7 +29690,7 @@
         </is>
       </c>
       <c r="G27" s="107" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
       <c r="H27" s="106" t="inlineStr">
         <is>
@@ -31491,7 +31430,7 @@
         </is>
       </c>
       <c r="E16" s="136" t="n">
-        <v>25.43</v>
+        <v>25.16</v>
       </c>
       <c r="F16" s="202" t="n">
         <v>0.4</v>
@@ -31735,7 +31674,7 @@
         </is>
       </c>
       <c r="E20" s="136" t="n">
-        <v>66.20999999999999</v>
+        <v>66.19</v>
       </c>
       <c r="F20" s="202" t="n">
         <v>0.4</v>
@@ -31918,7 +31857,7 @@
         </is>
       </c>
       <c r="E23" s="136" t="n">
-        <v>10.76</v>
+        <v>10.75</v>
       </c>
       <c r="F23" s="202" t="n">
         <v>0.4</v>
@@ -32040,7 +31979,7 @@
         </is>
       </c>
       <c r="E25" s="136" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
       <c r="F25" s="202" t="n">
         <v>0.4</v>
@@ -33021,7 +32960,7 @@
         </is>
       </c>
       <c r="E16" s="136" t="n">
-        <v>25.43</v>
+        <v>25.16</v>
       </c>
       <c r="F16" s="176" t="n">
         <v>0</v>
@@ -33161,7 +33100,7 @@
         </is>
       </c>
       <c r="E20" s="136" t="n">
-        <v>66.20999999999999</v>
+        <v>66.19</v>
       </c>
       <c r="F20" s="176" t="n">
         <v>0</v>
@@ -33266,7 +33205,7 @@
         </is>
       </c>
       <c r="E23" s="136" t="n">
-        <v>10.76</v>
+        <v>10.75</v>
       </c>
       <c r="F23" s="176" t="n">
         <v>0</v>
@@ -33336,7 +33275,7 @@
         </is>
       </c>
       <c r="E25" s="136" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
       <c r="F25" s="176" t="n">
         <v>0</v>

--- a/entregables_varones/METRADO_DRENAJE_PLUVIAL_CAR_VARONES_CON_COLECTOR.xlsx
+++ b/entregables_varones/METRADO_DRENAJE_PLUVIAL_CAR_VARONES_CON_COLECTOR.xlsx
@@ -5058,7 +5058,7 @@
       </c>
       <c r="C21" s="184" t="n"/>
       <c r="D21" s="190" t="n">
-        <v>42.45</v>
+        <v>42.66</v>
       </c>
       <c r="E21" s="188">
         <f>+'CONCRETO EN CUNETAS'!M34</f>
@@ -6025,7 +6025,7 @@
         <v>42.7</v>
       </c>
       <c r="D14" s="368" t="n">
-        <v>0.25</v>
+        <v>0.04</v>
       </c>
       <c r="E14" s="369">
         <f>C14-D14</f>
@@ -11242,7 +11242,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="31" t="n">
-        <v>42.45</v>
+        <v>42.66</v>
       </c>
       <c r="E20" s="31" t="n">
         <v>1.4</v>
@@ -11571,7 +11571,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="31" t="n">
-        <v>42.45</v>
+        <v>42.66</v>
       </c>
       <c r="E33" s="31" t="n">
         <v>1.4</v>
@@ -11938,7 +11938,7 @@
         <v>1</v>
       </c>
       <c r="D47" s="31" t="n">
-        <v>42.45</v>
+        <v>42.66</v>
       </c>
       <c r="E47" s="31" t="n">
         <v>1.4</v>
@@ -12341,7 +12341,7 @@
         <v>1</v>
       </c>
       <c r="D63" s="31" t="n">
-        <v>42.45</v>
+        <v>42.66</v>
       </c>
       <c r="E63" s="31" t="n">
         <v>0.6</v>
@@ -12686,7 +12686,7 @@
         <v>1</v>
       </c>
       <c r="D76" s="31" t="n">
-        <v>42.45</v>
+        <v>42.66</v>
       </c>
       <c r="E76" s="31" t="n">
         <v>0.8</v>
@@ -13123,7 +13123,7 @@
         <v>1</v>
       </c>
       <c r="D93" s="31" t="n">
-        <v>42.45</v>
+        <v>42.66</v>
       </c>
       <c r="E93" s="31" t="n">
         <v>0.6</v>
@@ -16818,7 +16818,7 @@
       </c>
       <c r="C10" s="377" t="inlineStr">
         <is>
-          <t>0+006.30</t>
+          <t>0+007.01</t>
         </is>
       </c>
       <c r="D10" s="378" t="inlineStr">
@@ -16846,7 +16846,7 @@
       </c>
       <c r="C11" s="377" t="inlineStr">
         <is>
-          <t>0+013.16</t>
+          <t>0+013.52</t>
         </is>
       </c>
       <c r="D11" s="378" t="inlineStr">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="C20" s="377" t="inlineStr">
         <is>
-          <t>0+006.30</t>
+          <t>0+007.01</t>
         </is>
       </c>
       <c r="D20" s="393" t="n">
@@ -20575,7 +20575,7 @@
         </is>
       </c>
       <c r="M34" s="80" t="n">
-        <v>17.55</v>
+        <v>17.67</v>
       </c>
       <c r="N34" s="319">
         <f>M34*M35*M36</f>
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="M38" s="14" t="n">
-        <v>42.45</v>
+        <v>42.66</v>
       </c>
       <c r="N38" s="325" t="n"/>
       <c r="O38" s="326" t="n"/>
@@ -20762,7 +20762,7 @@
         </is>
       </c>
       <c r="M40" s="80" t="n">
-        <v>6.45</v>
+        <v>6.66</v>
       </c>
       <c r="N40" s="319">
         <f>M40*M41*M42</f>
@@ -24001,7 +24001,7 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>4.75</v>
+        <v>4.91</v>
       </c>
       <c r="G61" s="251">
         <f>F61*F62</f>
@@ -24075,7 +24075,7 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>3.46</v>
+        <v>3.58</v>
       </c>
       <c r="G63" s="251">
         <f>F63*F64+F65</f>
@@ -24141,7 +24141,7 @@
         </is>
       </c>
       <c r="F65" s="14">
-        <f>6.45*0.4</f>
+        <f>6.66*0.4</f>
         <v/>
       </c>
       <c r="G65" s="315" t="n"/>
@@ -29690,7 +29690,7 @@
         </is>
       </c>
       <c r="G27" s="107" t="n">
-        <v>6.45</v>
+        <v>6.66</v>
       </c>
       <c r="H27" s="106" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         </is>
       </c>
       <c r="E25" s="136" t="n">
-        <v>6.45</v>
+        <v>6.66</v>
       </c>
       <c r="F25" s="202" t="n">
         <v>0.4</v>
@@ -33275,7 +33275,7 @@
         </is>
       </c>
       <c r="E25" s="136" t="n">
-        <v>6.45</v>
+        <v>6.66</v>
       </c>
       <c r="F25" s="176" t="n">
         <v>0</v>

--- a/entregables_varones/METRADO_DRENAJE_PLUVIAL_CAR_VARONES_CON_COLECTOR.xlsx
+++ b/entregables_varones/METRADO_DRENAJE_PLUVIAL_CAR_VARONES_CON_COLECTOR.xlsx
@@ -515,7 +515,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2474" uniqueCount="1332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2474" uniqueCount="1339">
   <si>
     <t xml:space="preserve">RESUMEN METRADOS DE DRENAJE PLUVIAL</t>
   </si>
@@ -4525,6 +4525,27 @@
   </si>
   <si>
     <t xml:space="preserve">DESAGREGADO LLORADEROS fila 64 (DL-02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borde engrosado de la abertura: perimetro (solo los 2 lados transversales, entre muros)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamina DP-06B: 2 x b; b = 0.60 es menor que la abertura de 0.70, en los lados largos el asiento es la cabeza del muro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGISTROS DE LIMPIEZA EN LA LOSA DEL COLECTOR - lamina DP-06B (borde engrosado 0.15 x 0.10 solo en los 2 lados transversales, entre muros: en los lados largos la abertura apoya en la cabeza de los muros; descuento de la abertura 0.70 x 0.70 en la losa superior)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registros RV-01 a RV-11: borde engrosado de la abertura (2 lados, entre muros)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP-06B, DD-01: 2 x 0.60 m por registro, en los 11 registros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamina DP-01 (ubicacion), DP-06B, DP-06D, DD-01 y DD-02 (detalle): contramarco L 1 1/2"x1 1/2"x1/8" anclado a la losa y a la cabeza de los muros, marco L 1 1/2"x1 1/2"x1/8" soldado a la tapa, tapa de concreto armado 0.68 x 0.68 x 0.08 con parrilla 3/8" @0.10 y asas; abertura de 0.70 x 0.70 sobre el colector de 0.60: en los lados largos apoya en la cabeza de los muros y el borde engrosado 0.15 x 0.10 va solo en los 2 lados transversales. El registro de la caja CL pertenece al expediente del Hogar de Refugio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bordes engrosados de abertura de registros RV-01 a RV-11 (2 lados, entre muros)</t>
   </si>
 </sst>
 </file>
@@ -7868,7 +7889,7 @@
       </c>
       <c r="D65" s="16" t="n">
         <f aca="false">+'PLANILLA GENERAL DE METRADOS'!K176</f>
-        <v>56.017129</v>
+        <v>55.720129</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12219,16 +12240,17 @@
         <v>31</v>
       </c>
       <c r="B40" s="150" t="s">
-        <v>588</v>
+        <v>1332</v>
       </c>
       <c r="C40" s="289" t="n">
-        <v>3</v>
+        <f aca="false">2*C10</f>
+        <v>1.2</v>
       </c>
       <c r="D40" s="290" t="s">
         <v>71</v>
       </c>
       <c r="E40" s="272" t="s">
-        <v>589</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13385,7 +13407,7 @@
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="296" t="s">
-        <v>649</v>
+        <v>1334</v>
       </c>
       <c r="B15" s="296"/>
       <c r="C15" s="296"/>
@@ -13450,14 +13472,14 @@
         <v>1</v>
       </c>
       <c r="B17" s="150" t="s">
-        <v>657</v>
+        <v>1335</v>
       </c>
       <c r="C17" s="269" t="s">
         <v>658</v>
       </c>
       <c r="D17" s="271" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$40</f>
-        <v>3.0</v>
+        <v>1.2</v>
       </c>
       <c r="E17" s="271" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$41</f>
@@ -13475,12 +13497,12 @@
       <c r="J17" s="22"/>
       <c r="K17" s="271" t="n">
         <f aca="false">D17*E17*F17*G17</f>
-        <v>0.495</v>
+        <v>0.198</v>
       </c>
       <c r="L17" s="22"/>
       <c r="M17" s="22"/>
       <c r="N17" s="272" t="s">
-        <v>659</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13546,7 +13568,7 @@
       </c>
       <c r="K19" s="295" t="n">
         <f aca="false">SUM(K17:K18)</f>
-        <v>-0.0439999999999999</v>
+        <v>-0.341</v>
       </c>
       <c r="L19" s="295" t="n">
         <f aca="false">SUM(L17:L18)</f>
@@ -13673,11 +13695,11 @@
       </c>
       <c r="H25" s="271" t="n">
         <f aca="false">K19</f>
-        <v>-0.0439999999999999</v>
+        <v>-0.341</v>
       </c>
       <c r="I25" s="298" t="n">
         <f aca="false">G25+H25</f>
-        <v>10.2529</v>
+        <v>9.9559</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17711,7 +17733,7 @@
       <c r="J176" s="26"/>
       <c r="K176" s="26" t="n">
         <f aca="false">SUM(J177:J189)</f>
-        <v>56.017129</v>
+        <v>55.720129</v>
       </c>
       <c r="L176" s="25" t="s">
         <v>25</v>
@@ -17941,7 +17963,7 @@
     <row r="188" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="27"/>
       <c r="B188" s="27" t="s">
-        <v>201</v>
+        <v>1338</v>
       </c>
       <c r="C188" s="28" t="n">
         <v>1</v>
@@ -17954,7 +17976,7 @@
       <c r="I188" s="28"/>
       <c r="J188" s="28" t="n">
         <f aca="false">'COLECTOR CONCRETO'!K17</f>
-        <v>0.495</v>
+        <v>0.198</v>
       </c>
       <c r="K188" s="28"/>
       <c r="L188" s="27"/>
@@ -19986,7 +20008,7 @@
     </row>
     <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="267" t="s">
-        <v>876</v>
+        <v>1337</v>
       </c>
       <c r="B7" s="267"/>
       <c r="C7" s="267"/>
@@ -21328,7 +21350,7 @@
       </c>
       <c r="D28" s="271" t="n">
         <f aca="false">SUM('PLANILLA GENERAL DE METRADOS'!J185:J189)</f>
-        <v>10.2529</v>
+        <v>9.9559</v>
       </c>
       <c r="E28" s="297" t="s">
         <v>802</v>
@@ -21341,7 +21363,7 @@
       </c>
       <c r="H28" s="298" t="n">
         <f aca="false">G28*$D$28</f>
-        <v>99.760717</v>
+        <v>96.870907</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21360,7 +21382,7 @@
       </c>
       <c r="H29" s="298" t="n">
         <f aca="false">G29*$D$28</f>
-        <v>5.331508</v>
+        <v>5.177068</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21379,7 +21401,7 @@
       </c>
       <c r="H30" s="298" t="n">
         <f aca="false">G30*$D$28</f>
-        <v>5.434037</v>
+        <v>5.276627</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21398,7 +21420,7 @@
       </c>
       <c r="H31" s="298" t="n">
         <f aca="false">G31*$D$28</f>
-        <v>1.9070394</v>
+        <v>1.8517974</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21417,7 +21439,7 @@
       </c>
       <c r="H32" s="298" t="n">
         <f aca="false">G32*$D$28</f>
-        <v>8.20232</v>
+        <v>7.96472</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21436,7 +21458,7 @@
       </c>
       <c r="H33" s="298" t="n">
         <f aca="false">G33*$D$28</f>
-        <v>8.20232</v>
+        <v>7.96472</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21455,7 +21477,7 @@
       </c>
       <c r="H34" s="298" t="n">
         <f aca="false">G34*$D$28</f>
-        <v>8.20232</v>
+        <v>7.96472</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21474,7 +21496,7 @@
       </c>
       <c r="H35" s="298" t="n">
         <f aca="false">G35*$D$28</f>
-        <v>8.20232</v>
+        <v>7.96472</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21493,7 +21515,7 @@
       </c>
       <c r="H36" s="298" t="n">
         <f aca="false">G36*$D$28</f>
-        <v>65.61856</v>
+        <v>63.71776</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/entregables_varones/METRADO_DRENAJE_PLUVIAL_CAR_VARONES_CON_COLECTOR.xlsx
+++ b/entregables_varones/METRADO_DRENAJE_PLUVIAL_CAR_VARONES_CON_COLECTOR.xlsx
@@ -515,7 +515,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2474" uniqueCount="1339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2474" uniqueCount="1423">
   <si>
     <t xml:space="preserve">RESUMEN METRADOS DE DRENAJE PLUVIAL</t>
   </si>
@@ -4546,6 +4546,258 @@
   </si>
   <si>
     <t xml:space="preserve">Bordes engrosados de abertura de registros RV-01 a RV-11 (2 lados, entre muros)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lado del rebaje de asiento de la tapa en la losa (0.70 x 0.70 x 0.08)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamina DP-06B rev. 02 (tapa ciega)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luz libre del registro bajo el rebaje (0.60 x 0.60)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamina DP-06B rev. 02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perimetro del encofrado lateral de la tapa (4 x 0.68)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asas de izaje por tapa (fierro liso 1/2" en cajuelas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desarrollo de cada asa de fierro liso 1/2"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamina DP-06B rev. 02: agarre 0.15 + 2 patas de 0.11 con gancho de 0.065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holgura entre la tapa y el rebaje (cada lado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bisel de los cantos superiores de la tapa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamina DP-06B rev. 02 (tapa ciega de concreto armado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamina DP-06B rev. 02 (= profundidad del rebaje)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asas de izaje de la tapa (en cajuelas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/2" liso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP-06B rev. 02: 2 asas de fierro liso 1/2" por tapa, desarrollo 0.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP-06B rev. 02: 7 + 7 barras de 3/8" @0.10, L = 0.62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACERO DE REFUERZO EN TAPAS, BORDES Y ASAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registros RV-01 a RV-11: descuento del rebaje y de la abertura en la losa superior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rebaje 0.70 x 0.70 x 0.08 + luz 0.60 x 0.60 en el resto (e equivalente)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAPA DE REGISTRO CIEGA DE CONCRETO ARMADO 0.68x0.68x0.08 (vaciada aparte en obra)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP-06B rev. 02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENCOFRADO LATERAL DE LA TAPA (molde de madera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">registros x 4 x 0.68 x 0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACERO EN TAPAS: PARRILLA 3/8" Y ASAS 1/2" LISO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hoja COLECTOR ACERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP-06B rev. 02; COLECTOR ACERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASIENTO DE LA TAPA: REBAJE DE CONCRETO 0.70 x 0.70 x 0.08 EN LA LOSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 por registro (concreto incluido en la losa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP-06B rev. 02; COLECTOR CONCRETO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLOCACION DE LA TAPA EN EL REBAJE (izaje con las asas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamina DP-01 (ubicacion) y DP-06B rev. 02 (detalle): tapa ciega de concreto armado 0.68 x 0.68 x 0.08, vaciada aparte en obra, con 2 asas de fierro liso 1/2", apoyada en un rebaje de concreto de 0.70 x 0.70 x 0.08 de la losa (luz libre 0.60 x 0.60). Sin marco ni contramarco metalico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.04.04.05.01 TAPA DE REGISTRO: encofrado lateral de la tapa (molde de madera, 6 usos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.04.04.05.01 TAPA DE REGISTRO: colocacion de la tapa en el rebaje y curado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAPA DE REGISTRO CIEGA DE CONCRETO ARMADO 0.68x0.68x0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cada tapa: concreto armado f'c=210 de 0.68 x 0.68 x 0.08 vaciado aparte en obra, parrilla 3/8" @0.10, 2 asas de fierro liso 1/2", asiento en rebaje de concreto 0.70 x 0.70 x 0.08 de la losa (luz libre 0.60 x 0.60) y refuerzo de borde 4 x 2 barras de 1/2". Sin marco ni contramarco metalico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANALISIS DE COSTO UNITARIO - TAPA DE REGISTRO CIEGA DE CONCRETO ARMADO 0.68x0.68x0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partida de Delphin 01.04.04.06.05.01 TAPA DE REGISTRO CIEGA DE CONCRETO ARMADO 0.68x0.68x0.08 (metrado 01.04.04.05.01, hojas COLECTOR REGISTROS Y TAPAS y COLECTOR ACERO). Tapa ciega de concreto armado vaciada aparte en obra sobre tablero, con parrilla 3/8" @0.10, 2 asas de fierro liso 1/2" en cajuelas y cantos biselados; se coloca en el rebaje de concreto de 0.70 x 0.70 x 0.08 de la losa (el rebaje y el borde engrosado se metran con el concreto del colector). Incluye el refuerzo de borde de la abertura (2 barras de 1/2" por lado). Sin marco ni contramarco metalico. Celda amarilla = dato; verde = formula. Precios sin IGV.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. CANTIDADES POR TAPA (hojas COLECTOR PARAMETROS, COLECTOR REGISTROS Y TAPAS y COLECTOR ACERO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numero de tapas (registros)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLECTOR REGISTROS Y TAPAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concreto f'c=210 por tapa: 0.68 x 0.68 x 0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encofrado lateral por tapa: 4 x 0.68 x 0.08 (molde de madera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tablero de vaciado: 0.80 x 0.80 x 1" = 6.89 p2 en 6 usos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acero 3/8" de la parrilla por tapa (7 + 7 barras, L = 0.62)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLECTOR ACERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acero 1/2" de borde de la abertura por registro (8 barras, L = 1.40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fierro liso 1/2" de las 2 asas por tapa (desarrollo 0.50 c/u)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desperdicio de acero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">criterio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cemento por m3 de concreto f'c=210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLECTOR INSUMOS (diseno de mezcla)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arena gruesa por m3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piedra chancada 1/2" por m3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agua por m3 (mezcla) + curado de la tapa (0.01 m3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mano de obra del concreto: operario / oficial / peon por m3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hh/m3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLECTOR INSUMOS (0.8 / 0.8 / 6.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peon por m3 de concreto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mano de obra del acero: operario / oficial por kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hh/kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mano de obra del encofrado: operario / oficial por m2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hh/m2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLECTOR INSUMOS (encofrado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colocacion de la tapa en el rebaje: operario + peon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hh/und</t>
+  </si>
+  <si>
+    <t xml:space="preserve">criterio de obra: 1 hh por tapa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.04.04.06.05.01 TAPA DE REGISTRO CIEGA DE CONCRETO ARMADO 0.68x0.68x0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.04.04.05.01 (hoja COLECTOR REGISTROS Y TAPAS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fierro liso 1/2" (asas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mismo precio por kg del acero corrugado (referencial): Sodimac Peru, Aceros Arequipa: 1/2" x 9 m S/ 36.50 y 3/8" x 9 m S/ 20.35 con IGV (ponderado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 % del costo de mano de obra (incluye mezcla y vibrado manual del concreto de la tapa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESAGREGADO DE LA PARTIDA 01.04.04.05.01 - TAPA DE REGISTRO CIEGA DE CONCRETO ARMADO 0.68x0.68x0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La partida se mide por unidad de registro. Cada tapa ciega de concreto armado se vacia aparte en obra y se coloca en el rebaje de 0.70 x 0.70 x 0.08 de la losa (luz libre 0.60 x 0.60). Sin marco ni contramarco metalico. Componentes tomados de las hojas COLECTOR REGISTROS Y TAPAS y COLECTOR ACERO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tapa ciega de concreto f'c=210: 0.68 x 0.68 x 0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lamina DP-06B rev. 02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENCOFRADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encofrado lateral de la tapa: 4 x 0.68 x 0.08 (molde de madera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subtotal encofrado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACERO DE REFUERZO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asas de izaje: 2 barras de fierro liso 1/2", desarrollo 0.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subtotal acero de refuerzo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encofrado lateral de tapas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acero en tapas, asas y bordes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No hay angulos, soldadura ni pintura: la tapa es ciega de concreto armado (lamina DP-06B rev. 02). El rebaje de asiento y el borde engrosado de la abertura se metran con el concreto de la losa del colector (hoja COLECTOR CONCRETO).</t>
   </si>
 </sst>
 </file>
@@ -5339,7 +5591,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="324">
+  <cellXfs count="325">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6636,6 +6888,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="170" fontId="5" fillId="6" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7889,7 +8145,7 @@
       </c>
       <c r="D65" s="16" t="n">
         <f aca="false">+'PLANILLA GENERAL DE METRADOS'!K176</f>
-        <v>55.720129</v>
+        <v>55.748729</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7967,7 +8223,7 @@
         <v>139</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>864</v>
+        <v>1372</v>
       </c>
       <c r="C71" s="15" t="s">
         <v>60</v>
@@ -12096,7 +12352,7 @@
         <v>71</v>
       </c>
       <c r="E31" s="272" t="s">
-        <v>575</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12113,7 +12369,7 @@
         <v>71</v>
       </c>
       <c r="E32" s="272" t="s">
-        <v>575</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12121,7 +12377,7 @@
         <v>24</v>
       </c>
       <c r="B33" s="150" t="s">
-        <v>577</v>
+        <v>1339</v>
       </c>
       <c r="C33" s="289" t="n">
         <v>0.7</v>
@@ -12130,7 +12386,7 @@
         <v>71</v>
       </c>
       <c r="E33" s="272" t="s">
-        <v>575</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12138,16 +12394,16 @@
         <v>25</v>
       </c>
       <c r="B34" s="150" t="s">
-        <v>871</v>
+        <v>1341</v>
       </c>
       <c r="C34" s="289" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="D34" s="290" t="s">
         <v>71</v>
       </c>
       <c r="E34" s="272" t="s">
-        <v>575</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12155,7 +12411,7 @@
         <v>26</v>
       </c>
       <c r="B35" s="150" t="s">
-        <v>579</v>
+        <v>1343</v>
       </c>
       <c r="C35" s="289" t="n">
         <v>2.72</v>
@@ -12164,7 +12420,7 @@
         <v>71</v>
       </c>
       <c r="E35" s="272" t="s">
-        <v>575</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12172,16 +12428,16 @@
         <v>27</v>
       </c>
       <c r="B36" s="150" t="s">
-        <v>872</v>
+        <v>1344</v>
       </c>
       <c r="C36" s="289" t="n">
-        <v>1.83</v>
+        <v>2.0</v>
       </c>
       <c r="D36" s="290" t="s">
-        <v>503</v>
+        <v>60</v>
       </c>
       <c r="E36" s="272" t="s">
-        <v>581</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12189,16 +12445,16 @@
         <v>28</v>
       </c>
       <c r="B37" s="150" t="s">
-        <v>873</v>
+        <v>1345</v>
       </c>
       <c r="C37" s="289" t="n">
-        <v>1.83</v>
+        <v>0.5</v>
       </c>
       <c r="D37" s="290" t="s">
-        <v>503</v>
+        <v>71</v>
       </c>
       <c r="E37" s="272" t="s">
-        <v>581</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12206,16 +12462,16 @@
         <v>29</v>
       </c>
       <c r="B38" s="150" t="s">
-        <v>874</v>
+        <v>1347</v>
       </c>
       <c r="C38" s="289" t="n">
-        <v>0.152</v>
+        <v>0.01</v>
       </c>
       <c r="D38" s="290" t="s">
-        <v>584</v>
+        <v>71</v>
       </c>
       <c r="E38" s="272" t="s">
-        <v>587</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12223,16 +12479,16 @@
         <v>30</v>
       </c>
       <c r="B39" s="150" t="s">
-        <v>875</v>
+        <v>1348</v>
       </c>
       <c r="C39" s="289" t="n">
-        <v>0.152</v>
+        <v>0.01</v>
       </c>
       <c r="D39" s="290" t="s">
-        <v>584</v>
+        <v>71</v>
       </c>
       <c r="E39" s="272" t="s">
-        <v>587</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13510,10 +13766,10 @@
         <v>2</v>
       </c>
       <c r="B18" s="150" t="s">
-        <v>660</v>
+        <v>1356</v>
       </c>
       <c r="C18" s="269" t="s">
-        <v>661</v>
+        <v>1357</v>
       </c>
       <c r="D18" s="271" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$33</f>
@@ -13524,8 +13780,8 @@
         <v>0.7</v>
       </c>
       <c r="F18" s="291" t="n">
-        <f aca="false">'COLECTOR PARAMETROS'!$C$13</f>
-        <v>0.1</v>
+        <f aca="false">'COLECTOR PARAMETROS'!$C$32+('COLECTOR PARAMETROS'!$C$13-'COLECTOR PARAMETROS'!$C$32)*('COLECTOR PARAMETROS'!$C$34/'COLECTOR PARAMETROS'!$C$33)^2</f>
+        <v>0.0946938775510204</v>
       </c>
       <c r="G18" s="299" t="n">
         <f aca="false">-'COLECTOR PARAMETROS'!$C$30</f>
@@ -13536,7 +13792,7 @@
       <c r="J18" s="22"/>
       <c r="K18" s="271" t="n">
         <f aca="false">D18*E18*F18*G18</f>
-        <v>-0.539</v>
+        <v>-0.5104</v>
       </c>
       <c r="L18" s="22"/>
       <c r="M18" s="22"/>
@@ -13568,7 +13824,7 @@
       </c>
       <c r="K19" s="295" t="n">
         <f aca="false">SUM(K17:K18)</f>
-        <v>-0.341</v>
+        <v>-0.3124</v>
       </c>
       <c r="L19" s="295" t="n">
         <f aca="false">SUM(L17:L18)</f>
@@ -13695,11 +13951,11 @@
       </c>
       <c r="H25" s="271" t="n">
         <f aca="false">K19</f>
-        <v>-0.341</v>
+        <v>-0.3124</v>
       </c>
       <c r="I25" s="298" t="n">
         <f aca="false">G25+H25</f>
-        <v>9.9559</v>
+        <v>9.9845</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17733,7 +17989,7 @@
       <c r="J176" s="26"/>
       <c r="K176" s="26" t="n">
         <f aca="false">SUM(J177:J189)</f>
-        <v>55.720129</v>
+        <v>55.748729</v>
       </c>
       <c r="L176" s="25" t="s">
         <v>25</v>
@@ -17997,7 +18253,7 @@
       <c r="I189" s="28"/>
       <c r="J189" s="28" t="n">
         <f aca="false">'COLECTOR CONCRETO'!K18</f>
-        <v>-0.539</v>
+        <v>-0.5104</v>
       </c>
       <c r="K189" s="28"/>
       <c r="L189" s="27"/>
@@ -18369,7 +18625,7 @@
         <v>139</v>
       </c>
       <c r="B207" s="25" t="s">
-        <v>864</v>
+        <v>1372</v>
       </c>
       <c r="C207" s="26"/>
       <c r="D207" s="26"/>
@@ -18411,7 +18667,7 @@
     <row r="209" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="27"/>
       <c r="B209" s="27" t="s">
-        <v>869</v>
+        <v>1373</v>
       </c>
       <c r="C209" s="28"/>
       <c r="D209" s="28"/>
@@ -18427,8 +18683,8 @@
     <row r="210" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="27"/>
       <c r="B210" s="27" t="str">
-        <f aca="false">"Totales para "&amp;K207&amp;" tapas: angulos "&amp;TEXT('COLECTOR REGISTROS Y TAPAS'!E27,"0.00")&amp;" kg; concreto "&amp;TEXT('COLECTOR REGISTROS Y TAPAS'!E29,"0.00")&amp;" m3; acero "&amp;TEXT('COLECTOR ACERO'!I25,"0.00")&amp;" kg; pintura "&amp;TEXT('COLECTOR REGISTROS Y TAPAS'!E30,"0.00")&amp;" m2"</f>
-        <v>Totales para 11 tapas: angulos 111.12 kg; concreto 0.41 m3; acero 190.71 kg; pintura 9.23 m2</v>
+        <f aca="false">"Totales para "&amp;K207&amp;" tapas: concreto "&amp;TEXT('COLECTOR REGISTROS Y TAPAS'!E28,"0.000")&amp;" m3; acero de tapas y asas "&amp;TEXT('COLECTOR REGISTROS Y TAPAS'!E27,"0.00")&amp;" kg; encofrado "&amp;TEXT('COLECTOR REGISTROS Y TAPAS'!E26,"0.00")&amp;" m2"</f>
+        <v>Totales para 11 tapas: concreto 0.407 m3; acero de tapas y asas 64.40 kg; encofrado 2.39 m2</v>
       </c>
       <c r="C210" s="28"/>
       <c r="D210" s="28"/>
@@ -19691,7 +19947,7 @@
         <v>53.4688</v>
       </c>
       <c r="V18" s="272" t="s">
-        <v>709</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19699,31 +19955,33 @@
         <v>3</v>
       </c>
       <c r="B19" s="150" t="s">
-        <v>710</v>
+        <v>1351</v>
       </c>
       <c r="C19" s="292" t="s">
-        <v>711</v>
+        <v>1352</v>
       </c>
       <c r="D19" s="269" t="s">
         <v>712</v>
       </c>
       <c r="E19" s="300" t="n">
-        <v>2</v>
+        <f aca="false">'COLECTOR PARAMETROS'!$C$36</f>
+        <v>2.0</v>
       </c>
       <c r="F19" s="299" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$30</f>
         <v>11.0</v>
       </c>
       <c r="G19" s="270" t="n">
-        <v>0.4</v>
+        <f aca="false">'COLECTOR PARAMETROS'!$C$37</f>
+        <v>0.5</v>
       </c>
       <c r="H19" s="271" t="n">
         <f aca="false">E19*F19*G19</f>
-        <v>8.8</v>
+        <v>11.0</v>
       </c>
       <c r="I19" s="291" t="n">
-        <f aca="false">'COLECTOR PARAMETROS'!$C$20</f>
-        <v>0.56</v>
+        <f aca="false">'COLECTOR PARAMETROS'!$C$21</f>
+        <v>0.994</v>
       </c>
       <c r="J19" s="22"/>
       <c r="K19" s="22"/>
@@ -19738,43 +19996,22 @@
       <c r="T19" s="22"/>
       <c r="U19" s="298" t="n">
         <f aca="false">H19*I19</f>
-        <v>4.928</v>
+        <v>10.934</v>
       </c>
       <c r="V19" s="272" t="s">
-        <v>713</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="269" t="n">
-        <v>4</v>
-      </c>
-      <c r="B20" s="150" t="s">
-        <v>714</v>
-      </c>
-      <c r="C20" s="292" t="s">
-        <v>347</v>
-      </c>
-      <c r="D20" s="269" t="s">
-        <v>715</v>
-      </c>
-      <c r="E20" s="300" t="n">
-        <v>8</v>
-      </c>
-      <c r="F20" s="299" t="n">
-        <f aca="false">'COLECTOR PARAMETROS'!$C$30</f>
-        <v>11.0</v>
-      </c>
-      <c r="G20" s="270" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H20" s="271" t="n">
-        <f aca="false">E20*F20*G20</f>
-        <v>17.6</v>
-      </c>
-      <c r="I20" s="291" t="n">
-        <f aca="false">'COLECTOR PARAMETROS'!$C$20</f>
-        <v>0.56</v>
-      </c>
+      <c r="A20" s="269"/>
+      <c r="B20" s="150"/>
+      <c r="C20" s="292"/>
+      <c r="D20" s="269"/>
+      <c r="E20" s="300"/>
+      <c r="F20" s="299"/>
+      <c r="G20" s="270"/>
+      <c r="H20" s="271"/>
+      <c r="I20" s="291"/>
       <c r="J20" s="22"/>
       <c r="K20" s="22"/>
       <c r="L20" s="22"/>
@@ -19786,13 +20023,8 @@
       <c r="R20" s="22"/>
       <c r="S20" s="22"/>
       <c r="T20" s="22"/>
-      <c r="U20" s="298" t="n">
-        <f aca="false">H20*I20</f>
-        <v>9.856</v>
-      </c>
-      <c r="V20" s="272" t="s">
-        <v>716</v>
-      </c>
+      <c r="U20" s="298"/>
+      <c r="V20" s="272"/>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="293" t="s">
@@ -19819,7 +20051,7 @@
       <c r="T21" s="294"/>
       <c r="U21" s="295" t="n">
         <f aca="false">SUM(U17:U20)</f>
-        <v>190.7136</v>
+        <v>186.8636</v>
       </c>
       <c r="V21" s="294"/>
     </row>
@@ -19880,7 +20112,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="297" t="s">
-        <v>720</v>
+        <v>1355</v>
       </c>
       <c r="C25" s="297"/>
       <c r="D25" s="297"/>
@@ -19890,15 +20122,15 @@
       </c>
       <c r="G25" s="271" t="n">
         <f aca="false">SUMIF(C17:C20,"3/8*",U17:U20)</f>
-        <v>68.2528</v>
+        <v>53.4688</v>
       </c>
       <c r="H25" s="271" t="n">
         <f aca="false">SUMIF(C17:C20,"1/2*",U17:U20)</f>
-        <v>122.4608</v>
+        <v>133.3948</v>
       </c>
       <c r="I25" s="298" t="n">
         <f aca="false">U21</f>
-        <v>190.7136</v>
+        <v>186.8636</v>
       </c>
     </row>
   </sheetData>
@@ -20008,7 +20240,7 @@
     </row>
     <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="267" t="s">
-        <v>1337</v>
+        <v>1369</v>
       </c>
       <c r="B7" s="267"/>
       <c r="C7" s="267"/>
@@ -20304,7 +20536,7 @@
         <v>1</v>
       </c>
       <c r="B25" s="150" t="s">
-        <v>877</v>
+        <v>1358</v>
       </c>
       <c r="C25" s="290" t="s">
         <v>60</v>
@@ -20317,7 +20549,7 @@
         <v>11.0</v>
       </c>
       <c r="F25" s="272" t="s">
-        <v>760</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20325,20 +20557,20 @@
         <v>2</v>
       </c>
       <c r="B26" s="150" t="s">
-        <v>142</v>
+        <v>1360</v>
       </c>
       <c r="C26" s="290" t="s">
-        <v>60</v>
+        <v>186</v>
       </c>
       <c r="D26" s="269" t="s">
-        <v>761</v>
+        <v>1361</v>
       </c>
       <c r="E26" s="298" t="n">
-        <f aca="false">E21</f>
-        <v>11.0</v>
+        <f aca="false">E21*'COLECTOR PARAMETROS'!$C$35*'COLECTOR PARAMETROS'!$C$32</f>
+        <v>2.3936</v>
       </c>
       <c r="F26" s="272" t="s">
-        <v>762</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20346,20 +20578,20 @@
         <v>3</v>
       </c>
       <c r="B27" s="150" t="s">
-        <v>763</v>
+        <v>1362</v>
       </c>
       <c r="C27" s="290" t="s">
         <v>50</v>
       </c>
       <c r="D27" s="269" t="s">
-        <v>878</v>
+        <v>1363</v>
       </c>
       <c r="E27" s="298" t="n">
-        <f aca="false">E21*('COLECTOR PARAMETROS'!$C$34*'COLECTOR PARAMETROS'!$C$36+'COLECTOR PARAMETROS'!$C$35*'COLECTOR PARAMETROS'!$C$37)</f>
-        <v>111.1176</v>
+        <f aca="false">'COLECTOR ACERO'!U18+'COLECTOR ACERO'!U19</f>
+        <v>64.4028</v>
       </c>
       <c r="F27" s="272" t="s">
-        <v>765</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20367,20 +20599,20 @@
         <v>4</v>
       </c>
       <c r="B28" s="150" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C28" s="290" t="s">
-        <v>60</v>
+        <v>185</v>
       </c>
       <c r="D28" s="269" t="s">
-        <v>759</v>
+        <v>769</v>
       </c>
       <c r="E28" s="298" t="n">
-        <f aca="false">E21</f>
-        <v>11.0</v>
+        <f aca="false">E21*'COLECTOR PARAMETROS'!$C$31*'COLECTOR PARAMETROS'!$C$31*'COLECTOR PARAMETROS'!$C$32</f>
+        <v>0.406912</v>
       </c>
       <c r="F28" s="272" t="s">
-        <v>767</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20388,20 +20620,20 @@
         <v>5</v>
       </c>
       <c r="B29" s="150" t="s">
-        <v>768</v>
+        <v>1365</v>
       </c>
       <c r="C29" s="290" t="s">
-        <v>185</v>
+        <v>60</v>
       </c>
       <c r="D29" s="269" t="s">
-        <v>769</v>
+        <v>1366</v>
       </c>
       <c r="E29" s="298" t="n">
-        <f aca="false">E21*'COLECTOR PARAMETROS'!$C$31*'COLECTOR PARAMETROS'!$C$31*'COLECTOR PARAMETROS'!$C$32</f>
-        <v>0.406912</v>
+        <f aca="false">E21</f>
+        <v>11.0</v>
       </c>
       <c r="F29" s="272" t="s">
-        <v>767</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20409,20 +20641,20 @@
         <v>6</v>
       </c>
       <c r="B30" s="150" t="s">
-        <v>152</v>
+        <v>1368</v>
       </c>
       <c r="C30" s="290" t="s">
-        <v>186</v>
+        <v>60</v>
       </c>
       <c r="D30" s="269" t="s">
-        <v>879</v>
+        <v>759</v>
       </c>
       <c r="E30" s="298" t="n">
-        <f aca="false">E21*('COLECTOR PARAMETROS'!$C$34*'COLECTOR PARAMETROS'!$C$38+'COLECTOR PARAMETROS'!$C$35*'COLECTOR PARAMETROS'!$C$39)</f>
-        <v>9.22944</v>
+        <f aca="false">E21</f>
+        <v>11.0</v>
       </c>
       <c r="F30" s="272" t="s">
-        <v>771</v>
+        <v>1359</v>
       </c>
     </row>
   </sheetData>
@@ -21350,7 +21582,7 @@
       </c>
       <c r="D28" s="271" t="n">
         <f aca="false">SUM('PLANILLA GENERAL DE METRADOS'!J185:J189)</f>
-        <v>9.9559</v>
+        <v>9.9845</v>
       </c>
       <c r="E28" s="297" t="s">
         <v>802</v>
@@ -21363,7 +21595,7 @@
       </c>
       <c r="H28" s="298" t="n">
         <f aca="false">G28*$D$28</f>
-        <v>96.870907</v>
+        <v>97.149185</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21382,7 +21614,7 @@
       </c>
       <c r="H29" s="298" t="n">
         <f aca="false">G29*$D$28</f>
-        <v>5.177068</v>
+        <v>5.19194</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21401,7 +21633,7 @@
       </c>
       <c r="H30" s="298" t="n">
         <f aca="false">G30*$D$28</f>
-        <v>5.276627</v>
+        <v>5.291785</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21420,7 +21652,7 @@
       </c>
       <c r="H31" s="298" t="n">
         <f aca="false">G31*$D$28</f>
-        <v>1.8517974</v>
+        <v>1.857117</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21439,7 +21671,7 @@
       </c>
       <c r="H32" s="298" t="n">
         <f aca="false">G32*$D$28</f>
-        <v>7.96472</v>
+        <v>7.9876</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21458,7 +21690,7 @@
       </c>
       <c r="H33" s="298" t="n">
         <f aca="false">G33*$D$28</f>
-        <v>7.96472</v>
+        <v>7.9876</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21477,7 +21709,7 @@
       </c>
       <c r="H34" s="298" t="n">
         <f aca="false">G34*$D$28</f>
-        <v>7.96472</v>
+        <v>7.9876</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21496,7 +21728,7 @@
       </c>
       <c r="H35" s="298" t="n">
         <f aca="false">G35*$D$28</f>
-        <v>7.96472</v>
+        <v>7.9876</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21515,7 +21747,7 @@
       </c>
       <c r="H36" s="298" t="n">
         <f aca="false">G36*$D$28</f>
-        <v>63.71776</v>
+        <v>63.9008</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22014,27 +22246,27 @@
         <v>10</v>
       </c>
       <c r="B60" s="297" t="s">
-        <v>899</v>
+        <v>1370</v>
       </c>
       <c r="C60" s="290" t="s">
-        <v>50</v>
+        <v>186</v>
       </c>
       <c r="D60" s="271" t="n">
-        <f aca="false">'COLECTOR REGISTROS Y TAPAS'!E27</f>
-        <v>111.1176</v>
+        <f aca="false">'COLECTOR REGISTROS Y TAPAS'!E26</f>
+        <v>2.3936</v>
       </c>
       <c r="E60" s="297" t="s">
-        <v>901</v>
+        <v>817</v>
       </c>
       <c r="F60" s="290" t="s">
-        <v>50</v>
+        <v>818</v>
       </c>
       <c r="G60" s="289" t="n">
-        <v>1.05</v>
+        <v>0.7067</v>
       </c>
       <c r="H60" s="298" t="n">
         <f aca="false">G60*$D$60</f>
-        <v>116.67348</v>
+        <v>1.69155712</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22043,17 +22275,17 @@
       <c r="C61" s="22"/>
       <c r="D61" s="22"/>
       <c r="E61" s="297" t="s">
-        <v>836</v>
+        <v>819</v>
       </c>
       <c r="F61" s="290" t="s">
         <v>50</v>
       </c>
       <c r="G61" s="289" t="n">
-        <v>0.03</v>
+        <v>0.0333</v>
       </c>
       <c r="H61" s="298" t="n">
         <f aca="false">G61*$D$60</f>
-        <v>3.333528</v>
+        <v>0.07970688</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22068,11 +22300,11 @@
         <v>811</v>
       </c>
       <c r="G62" s="289" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="H62" s="298" t="n">
         <f aca="false">G62*$D$60</f>
-        <v>11.11176</v>
+        <v>1.91488</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22087,11 +22319,11 @@
         <v>811</v>
       </c>
       <c r="G63" s="289" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="H63" s="298" t="n">
         <f aca="false">G63*$D$60</f>
-        <v>11.11176</v>
+        <v>1.91488</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22099,27 +22331,27 @@
         <v>11</v>
       </c>
       <c r="B64" s="297" t="s">
-        <v>900</v>
+        <v>1371</v>
       </c>
       <c r="C64" s="290" t="s">
-        <v>186</v>
+        <v>60</v>
       </c>
       <c r="D64" s="271" t="n">
         <f aca="false">'COLECTOR REGISTROS Y TAPAS'!E30</f>
-        <v>9.22944</v>
+        <v>11.0</v>
       </c>
       <c r="E64" s="297" t="s">
-        <v>838</v>
+        <v>810</v>
       </c>
       <c r="F64" s="290" t="s">
-        <v>839</v>
+        <v>811</v>
       </c>
       <c r="G64" s="289" t="n">
-        <v>0.08</v>
+        <v>1.0</v>
       </c>
       <c r="H64" s="298" t="n">
         <f aca="false">G64*$D$64</f>
-        <v>0.7383552</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22128,17 +22360,17 @@
       <c r="C65" s="22"/>
       <c r="D65" s="22"/>
       <c r="E65" s="297" t="s">
-        <v>840</v>
+        <v>813</v>
       </c>
       <c r="F65" s="290" t="s">
-        <v>839</v>
+        <v>811</v>
       </c>
       <c r="G65" s="289" t="n">
-        <v>0.08</v>
+        <v>1.0</v>
       </c>
       <c r="H65" s="298" t="n">
         <f aca="false">G65*$D$64</f>
-        <v>0.7383552</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22147,17 +22379,17 @@
       <c r="C66" s="22"/>
       <c r="D66" s="22"/>
       <c r="E66" s="297" t="s">
-        <v>902</v>
+        <v>806</v>
       </c>
       <c r="F66" s="290" t="s">
-        <v>60</v>
+        <v>185</v>
       </c>
       <c r="G66" s="289" t="n">
-        <v>0.25</v>
+        <v>0.01</v>
       </c>
       <c r="H66" s="298" t="n">
         <f aca="false">G66*$D$64</f>
-        <v>2.30736</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22165,38 +22397,20 @@
       <c r="B67" s="305"/>
       <c r="C67" s="22"/>
       <c r="D67" s="22"/>
-      <c r="E67" s="297" t="s">
-        <v>903</v>
-      </c>
-      <c r="F67" s="290" t="s">
-        <v>839</v>
-      </c>
-      <c r="G67" s="289" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="H67" s="298" t="n">
-        <f aca="false">G67*$D$64</f>
-        <v>0.22150656</v>
-      </c>
+      <c r="E67" s="297"/>
+      <c r="F67" s="290"/>
+      <c r="G67" s="289"/>
+      <c r="H67" s="298"/>
     </row>
     <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="22"/>
       <c r="B68" s="305"/>
       <c r="C68" s="22"/>
       <c r="D68" s="22"/>
-      <c r="E68" s="297" t="s">
-        <v>810</v>
-      </c>
-      <c r="F68" s="290" t="s">
-        <v>811</v>
-      </c>
-      <c r="G68" s="289" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H68" s="298" t="n">
-        <f aca="false">G68*$D$64</f>
-        <v>3.691776</v>
-      </c>
+      <c r="E68" s="297"/>
+      <c r="F68" s="290"/>
+      <c r="G68" s="289"/>
+      <c r="H68" s="298"/>
     </row>
     <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="269" t="n">
@@ -23340,7 +23554,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="318" width="6"/>
@@ -23351,16 +23565,16 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="306" t="s">
-        <v>967</v>
-      </c>
-      <c r="B1" s="306"/>
-      <c r="C1" s="306"/>
-      <c r="D1" s="306"/>
-      <c r="E1" s="306"/>
-      <c r="F1" s="306"/>
-      <c r="G1" s="306"/>
-      <c r="H1" s="306"/>
+      <c r="A1" s="277" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B1" s="277"/>
+      <c r="C1" s="277"/>
+      <c r="D1" s="277"/>
+      <c r="E1" s="277"/>
+      <c r="F1" s="277"/>
+      <c r="G1" s="277"/>
+      <c r="H1" s="277"/>
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="307" t="s">
@@ -23423,2017 +23637,949 @@
       <c r="H5" s="266"/>
     </row>
     <row r="7" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="309" t="s">
-        <v>968</v>
-      </c>
-      <c r="B7" s="309"/>
-      <c r="C7" s="309"/>
-      <c r="D7" s="309"/>
-      <c r="E7" s="309"/>
-      <c r="F7" s="309"/>
-      <c r="G7" s="309"/>
-      <c r="H7" s="309"/>
+      <c r="A7" s="281" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B7" s="281"/>
+      <c r="C7" s="281"/>
+      <c r="D7" s="281"/>
+      <c r="E7" s="281"/>
+      <c r="F7" s="281"/>
+      <c r="G7" s="281"/>
+      <c r="H7" s="281"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="310" t="s">
-        <v>969</v>
-      </c>
-      <c r="B9" s="310"/>
-      <c r="C9" s="310"/>
-      <c r="D9" s="310"/>
-      <c r="E9" s="310"/>
-      <c r="F9" s="310"/>
-      <c r="G9" s="310"/>
-      <c r="H9" s="310"/>
+      <c r="A9" s="294" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B9" s="294"/>
+      <c r="C9" s="294"/>
+      <c r="D9" s="294"/>
+      <c r="E9" s="294"/>
+      <c r="F9" s="294"/>
+      <c r="G9" s="294"/>
+      <c r="H9" s="294"/>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="311" t="s">
+      <c r="A10" s="282" t="s">
         <v>309</v>
       </c>
-      <c r="B10" s="311" t="s">
-        <v>970</v>
-      </c>
-      <c r="C10" s="311" t="s">
+      <c r="B10" s="282" t="s">
+        <v>917</v>
+      </c>
+      <c r="C10" s="282" t="s">
         <v>170</v>
       </c>
-      <c r="D10" s="311" t="s">
-        <v>971</v>
-      </c>
-      <c r="E10" s="311" t="s">
-        <v>972</v>
-      </c>
-      <c r="F10" s="311" t="s">
+      <c r="D10" s="282" t="s">
+        <v>271</v>
+      </c>
+      <c r="E10" s="282"/>
+      <c r="F10" s="282"/>
+      <c r="G10" s="282"/>
+      <c r="H10" s="282" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="283" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B11" s="149" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C11" s="285" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="306" t="n">
+        <f aca="false">'COLECTOR REGISTROS Y TAPAS'!E21</f>
+        <v>11.0</v>
+      </c>
+      <c r="E11" s="295"/>
+      <c r="F11" s="295"/>
+      <c r="G11" s="295"/>
+      <c r="H11" s="149" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="283" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B12" s="149" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C12" s="285" t="s">
+        <v>185</v>
+      </c>
+      <c r="D12" s="306" t="n">
+        <f aca="false">'COLECTOR PARAMETROS'!$C$31^2*'COLECTOR PARAMETROS'!$C$32</f>
+        <v>0.036992</v>
+      </c>
+      <c r="E12" s="295"/>
+      <c r="F12" s="295"/>
+      <c r="G12" s="295"/>
+      <c r="H12" s="149" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="283" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B13" s="149" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C13" s="285" t="s">
+        <v>186</v>
+      </c>
+      <c r="D13" s="306" t="n">
+        <f aca="false">'COLECTOR PARAMETROS'!$C$35*'COLECTOR PARAMETROS'!$C$32</f>
+        <v>0.2176</v>
+      </c>
+      <c r="E13" s="295"/>
+      <c r="F13" s="295"/>
+      <c r="G13" s="295"/>
+      <c r="H13" s="149" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="283" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B14" s="149" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C14" s="285" t="s">
+        <v>818</v>
+      </c>
+      <c r="D14" s="324" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E14" s="295"/>
+      <c r="F14" s="295"/>
+      <c r="G14" s="295"/>
+      <c r="H14" s="149" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="283" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B15" s="149" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C15" s="285" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="306" t="n">
+        <f aca="false">'COLECTOR ACERO'!U18/'COLECTOR ACERO'!F18</f>
+        <v>4.8608</v>
+      </c>
+      <c r="E15" s="295"/>
+      <c r="F15" s="295"/>
+      <c r="G15" s="295"/>
+      <c r="H15" s="149" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="283" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B16" s="149" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C16" s="285" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="306" t="n">
+        <f aca="false">'COLECTOR ACERO'!U17/'COLECTOR ACERO'!F17</f>
+        <v>11.1328</v>
+      </c>
+      <c r="E16" s="295"/>
+      <c r="F16" s="295"/>
+      <c r="G16" s="295"/>
+      <c r="H16" s="149" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="283" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B17" s="149" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C17" s="285" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="306" t="n">
+        <f aca="false">'COLECTOR ACERO'!U19/'COLECTOR ACERO'!F19</f>
+        <v>0.994</v>
+      </c>
+      <c r="E17" s="295"/>
+      <c r="F17" s="295"/>
+      <c r="G17" s="295"/>
+      <c r="H17" s="149" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="283" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B18" s="149" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C18" s="285" t="s">
+        <v>511</v>
+      </c>
+      <c r="D18" s="324" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E18" s="295"/>
+      <c r="F18" s="295"/>
+      <c r="G18" s="295"/>
+      <c r="H18" s="149" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="283" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B19" s="149" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C19" s="285" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D19" s="306" t="n">
+        <f aca="false">'COLECTOR INSUMOS'!G10</f>
+        <v>9.73</v>
+      </c>
+      <c r="E19" s="295"/>
+      <c r="F19" s="295"/>
+      <c r="G19" s="295"/>
+      <c r="H19" s="149" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="283" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B20" s="149" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C20" s="285" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D20" s="306" t="n">
+        <f aca="false">'COLECTOR INSUMOS'!G11</f>
+        <v>0.52</v>
+      </c>
+      <c r="E20" s="295"/>
+      <c r="F20" s="295"/>
+      <c r="G20" s="295"/>
+      <c r="H20" s="149" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="283" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B21" s="149" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C21" s="285" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D21" s="306" t="n">
+        <f aca="false">'COLECTOR INSUMOS'!G12</f>
+        <v>0.53</v>
+      </c>
+      <c r="E21" s="295"/>
+      <c r="F21" s="295"/>
+      <c r="G21" s="295"/>
+      <c r="H21" s="149" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="283" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B22" s="149" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C22" s="285" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D22" s="306" t="n">
+        <f aca="false">'COLECTOR INSUMOS'!G13</f>
+        <v>0.186</v>
+      </c>
+      <c r="E22" s="295"/>
+      <c r="F22" s="295"/>
+      <c r="G22" s="295"/>
+      <c r="H22" s="149" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="283" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B23" s="149" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C23" s="285" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D23" s="306" t="n">
+        <f aca="false">'COLECTOR INSUMOS'!G16</f>
+        <v>0.8</v>
+      </c>
+      <c r="E23" s="295"/>
+      <c r="F23" s="295"/>
+      <c r="G23" s="295"/>
+      <c r="H23" s="149" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="283" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B24" s="149" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C24" s="285" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D24" s="306" t="n">
+        <f aca="false">'COLECTOR INSUMOS'!G18</f>
+        <v>6.4</v>
+      </c>
+      <c r="E24" s="295"/>
+      <c r="F24" s="295"/>
+      <c r="G24" s="295"/>
+      <c r="H24" s="149" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="283" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B25" s="149" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C25" s="285" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D25" s="306" t="n">
+        <f aca="false">'COLECTOR INSUMOS'!G44</f>
+        <v>0.032</v>
+      </c>
+      <c r="E25" s="295"/>
+      <c r="F25" s="295"/>
+      <c r="G25" s="295"/>
+      <c r="H25" s="149" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="283" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B26" s="149" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C26" s="285" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D26" s="324" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E26" s="295"/>
+      <c r="F26" s="295"/>
+      <c r="G26" s="295"/>
+      <c r="H26" s="149" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="283" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B27" s="149" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C27" s="285" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D27" s="324" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E27" s="295"/>
+      <c r="F27" s="295"/>
+      <c r="G27" s="295"/>
+      <c r="H27" s="149" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="294" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B29" s="294"/>
+      <c r="C29" s="294"/>
+      <c r="D29" s="294"/>
+      <c r="E29" s="294"/>
+      <c r="F29" s="294"/>
+      <c r="G29" s="294"/>
+      <c r="H29" s="294"/>
+    </row>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="294" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B30" s="294"/>
+      <c r="C30" s="295" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D30" s="295"/>
+      <c r="E30" s="295"/>
+      <c r="F30" s="295"/>
+      <c r="G30" s="295"/>
+      <c r="H30" s="295"/>
+    </row>
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="294" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B31" s="294"/>
+      <c r="C31" s="295" t="s">
+        <v>1406</v>
+      </c>
+      <c r="D31" s="295"/>
+      <c r="E31" s="295"/>
+      <c r="F31" s="295"/>
+      <c r="G31" s="295"/>
+      <c r="H31" s="295"/>
+    </row>
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="294" t="s">
+        <v>490</v>
+      </c>
+      <c r="B32" s="294"/>
+      <c r="C32" s="295" t="s">
+        <v>60</v>
+      </c>
+      <c r="D32" s="295"/>
+      <c r="E32" s="295"/>
+      <c r="F32" s="295"/>
+      <c r="G32" s="295"/>
+      <c r="H32" s="295"/>
+    </row>
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="294" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B33" s="294"/>
+      <c r="C33" s="290" t="n">
+        <f aca="false">'COLECTOR REGISTROS Y TAPAS'!E25</f>
+        <v>11.0</v>
+      </c>
+      <c r="D33" s="290"/>
+      <c r="E33" s="290"/>
+      <c r="F33" s="290"/>
+      <c r="G33" s="290"/>
+      <c r="H33" s="290"/>
+    </row>
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="294" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B34" s="294"/>
+      <c r="C34" s="290" t="n">
+        <f aca="false">8/E37</f>
+        <v>4.57855332366343</v>
+      </c>
+      <c r="D34" s="290"/>
+      <c r="E34" s="290"/>
+      <c r="F34" s="290"/>
+      <c r="G34" s="290"/>
+      <c r="H34" s="290"/>
+    </row>
+    <row r="35" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="282" t="s">
+        <v>309</v>
+      </c>
+      <c r="B35" s="282" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C35" s="282" t="s">
+        <v>170</v>
+      </c>
+      <c r="D35" s="282" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E35" s="282" t="s">
         <v>973</v>
       </c>
-      <c r="G10" s="311" t="s">
-        <v>970</v>
-      </c>
-      <c r="H10" s="311" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="312" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" s="313" t="s">
-        <v>974</v>
-      </c>
-      <c r="C11" s="315" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="271" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E25</f>
-        <v>11.0</v>
-      </c>
-      <c r="E11" s="319" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E21</f>
-        <v>11.0</v>
-      </c>
-      <c r="F11" s="320" t="n">
-        <f aca="false">D11/E11</f>
+      <c r="F35" s="282" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G35" s="282" t="s">
+        <v>998</v>
+      </c>
+      <c r="H35" s="282" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21"/>
+      <c r="B36" s="294" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C36" s="294"/>
+      <c r="D36" s="294"/>
+      <c r="E36" s="294"/>
+      <c r="F36" s="294"/>
+      <c r="G36" s="294"/>
+      <c r="H36" s="294"/>
+    </row>
+    <row r="37" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="283" t="n">
         <v>1.0</v>
       </c>
-      <c r="G11" s="312" t="s">
-        <v>975</v>
-      </c>
-      <c r="H11" s="313" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="312" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" s="313" t="s">
-        <v>977</v>
-      </c>
-      <c r="C12" s="315" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="271" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E26</f>
-        <v>11.0</v>
-      </c>
-      <c r="E12" s="319" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E21</f>
-        <v>11.0</v>
-      </c>
-      <c r="F12" s="320" t="n">
-        <f aca="false">D12/E12</f>
+      <c r="B37" s="295" t="s">
+        <v>810</v>
+      </c>
+      <c r="C37" s="285" t="s">
+        <v>811</v>
+      </c>
+      <c r="D37" s="306" t="n">
+        <f aca="false">E37*$C$34/8</f>
         <v>1.0</v>
       </c>
-      <c r="G12" s="312" t="s">
-        <v>978</v>
-      </c>
-      <c r="H12" s="313" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="312" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" s="313" t="s">
-        <v>980</v>
-      </c>
-      <c r="C13" s="315" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="271" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E27</f>
-        <v>111.1176</v>
-      </c>
-      <c r="E13" s="319" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E21</f>
-        <v>11.0</v>
-      </c>
-      <c r="F13" s="320" t="n">
-        <f aca="false">D13/E13</f>
-        <v>10.1016</v>
-      </c>
-      <c r="G13" s="312" t="s">
-        <v>981</v>
-      </c>
-      <c r="H13" s="313" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="312" t="n">
-        <v>4</v>
-      </c>
-      <c r="B14" s="313" t="s">
-        <v>983</v>
-      </c>
-      <c r="C14" s="315" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="271" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E28</f>
-        <v>11.0</v>
-      </c>
-      <c r="E14" s="319" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E21</f>
-        <v>11.0</v>
-      </c>
-      <c r="F14" s="320" t="n">
-        <f aca="false">D14/E14</f>
-        <v>1.0</v>
-      </c>
-      <c r="G14" s="312" t="s">
-        <v>984</v>
-      </c>
-      <c r="H14" s="313" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="312" t="n">
-        <v>5</v>
-      </c>
-      <c r="B15" s="313" t="s">
-        <v>985</v>
-      </c>
-      <c r="C15" s="315" t="s">
-        <v>185</v>
-      </c>
-      <c r="D15" s="320" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E29</f>
-        <v>0.406912</v>
-      </c>
-      <c r="E15" s="319" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E21</f>
-        <v>11.0</v>
-      </c>
-      <c r="F15" s="320" t="n">
-        <f aca="false">D15/E15</f>
-        <v>0.036992</v>
-      </c>
-      <c r="G15" s="312" t="s">
-        <v>986</v>
-      </c>
-      <c r="H15" s="313" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="312" t="n">
-        <v>6</v>
-      </c>
-      <c r="B16" s="313" t="s">
-        <v>988</v>
-      </c>
-      <c r="C16" s="315" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="271" t="n">
-        <f aca="false">+'COLECTOR ACERO'!I25</f>
-        <v>190.7136</v>
-      </c>
-      <c r="E16" s="319" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E21</f>
-        <v>11.0</v>
-      </c>
-      <c r="F16" s="320" t="n">
-        <f aca="false">D16/E16</f>
-        <v>17.3376</v>
-      </c>
-      <c r="G16" s="312" t="s">
-        <v>989</v>
-      </c>
-      <c r="H16" s="313" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="312" t="n">
-        <v>7</v>
-      </c>
-      <c r="B17" s="313" t="s">
-        <v>991</v>
-      </c>
-      <c r="C17" s="315" t="s">
-        <v>186</v>
-      </c>
-      <c r="D17" s="271" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E30</f>
-        <v>9.22944</v>
-      </c>
-      <c r="E17" s="319" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E21</f>
-        <v>11.0</v>
-      </c>
-      <c r="F17" s="320" t="n">
-        <f aca="false">D17/E17</f>
-        <v>0.83904</v>
-      </c>
-      <c r="G17" s="312" t="s">
-        <v>992</v>
-      </c>
-      <c r="H17" s="313" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="310" t="s">
-        <v>994</v>
-      </c>
-      <c r="B19" s="310"/>
-      <c r="C19" s="310"/>
-      <c r="D19" s="310"/>
-      <c r="E19" s="310"/>
-      <c r="F19" s="310"/>
-      <c r="G19" s="310"/>
-      <c r="H19" s="310"/>
-    </row>
-    <row r="20" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="311" t="s">
-        <v>309</v>
-      </c>
-      <c r="B20" s="311" t="s">
-        <v>797</v>
-      </c>
-      <c r="C20" s="311" t="s">
-        <v>170</v>
-      </c>
-      <c r="D20" s="311" t="s">
-        <v>995</v>
-      </c>
-      <c r="E20" s="311" t="s">
-        <v>996</v>
-      </c>
-      <c r="F20" s="311" t="s">
-        <v>997</v>
-      </c>
-      <c r="G20" s="311" t="s">
-        <v>998</v>
-      </c>
-      <c r="H20" s="311" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="312" t="s">
-        <v>1000</v>
-      </c>
-      <c r="B21" s="310" t="s">
-        <v>1001</v>
-      </c>
-      <c r="C21" s="310"/>
-      <c r="D21" s="310"/>
-      <c r="E21" s="310"/>
-      <c r="F21" s="310"/>
-      <c r="G21" s="310"/>
-      <c r="H21" s="310"/>
-    </row>
-    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="317"/>
-      <c r="B22" s="314" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C22" s="315" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" s="320" t="n">
-        <f aca="false">'COLECTOR PARAMETROS'!C34*'COLECTOR PARAMETROS'!C36</f>
-        <v>5.124</v>
-      </c>
-      <c r="E22" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G60</f>
-        <v>1.05</v>
-      </c>
-      <c r="F22" s="320" t="n">
-        <f aca="false">D22*E22</f>
-        <v>5.3802</v>
-      </c>
-      <c r="G22" s="271" t="n">
-        <f aca="false">F22*SUMIF($B$68:$B$93,B22,$F$68:$F$93)</f>
-        <v>16.571016</v>
-      </c>
-      <c r="H22" s="313" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="317"/>
-      <c r="B23" s="314" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C23" s="315" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23" s="320" t="n">
-        <f aca="false">'COLECTOR PARAMETROS'!C35*'COLECTOR PARAMETROS'!C37</f>
-        <v>4.9776</v>
-      </c>
-      <c r="E23" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G60</f>
-        <v>1.05</v>
-      </c>
-      <c r="F23" s="320" t="n">
-        <f aca="false">D23*E23</f>
-        <v>5.22648</v>
-      </c>
-      <c r="G23" s="271" t="n">
-        <f aca="false">F23*SUMIF($B$68:$B$93,B23,$F$68:$F$93)</f>
-        <v>16.0975584</v>
-      </c>
-      <c r="H23" s="313" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="317"/>
-      <c r="B24" s="314" t="s">
-        <v>1005</v>
-      </c>
-      <c r="C24" s="315" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" s="320" t="n">
-        <f aca="false">F13</f>
-        <v>10.1016</v>
-      </c>
-      <c r="E24" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G61</f>
-        <v>0.03</v>
-      </c>
-      <c r="F24" s="320" t="n">
-        <f aca="false">D24*E24</f>
-        <v>0.303048</v>
-      </c>
-      <c r="G24" s="271" t="n">
-        <f aca="false">F24*SUMIF($B$68:$B$93,B24,$F$68:$F$93)</f>
-        <v>5.64578424</v>
-      </c>
-      <c r="H24" s="313" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="317"/>
-      <c r="B25" s="314" t="s">
-        <v>810</v>
-      </c>
-      <c r="C25" s="315" t="s">
-        <v>811</v>
-      </c>
-      <c r="D25" s="320" t="n">
-        <f aca="false">F13</f>
-        <v>10.1016</v>
-      </c>
-      <c r="E25" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G62</f>
-        <v>0.1</v>
-      </c>
-      <c r="F25" s="320" t="n">
-        <f aca="false">D25*E25</f>
-        <v>1.01016</v>
-      </c>
-      <c r="G25" s="271" t="n">
-        <f aca="false">F25*SUMIF($B$68:$B$93,B25,$F$68:$F$93)</f>
-        <v>29.244132</v>
-      </c>
-      <c r="H25" s="313" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="317"/>
-      <c r="B26" s="314" t="s">
-        <v>812</v>
-      </c>
-      <c r="C26" s="315" t="s">
-        <v>811</v>
-      </c>
-      <c r="D26" s="320" t="n">
-        <f aca="false">F13</f>
-        <v>10.1016</v>
-      </c>
-      <c r="E26" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G63</f>
-        <v>0.1</v>
-      </c>
-      <c r="F26" s="320" t="n">
-        <f aca="false">D26*E26</f>
-        <v>1.01016</v>
-      </c>
-      <c r="G26" s="271" t="n">
-        <f aca="false">F26*SUMIF($B$68:$B$93,B26,$F$68:$F$93)</f>
-        <v>22.9104288</v>
-      </c>
-      <c r="H26" s="313" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="317"/>
-      <c r="B27" s="314" t="s">
-        <v>1007</v>
-      </c>
-      <c r="C27" s="315" t="s">
-        <v>808</v>
-      </c>
-      <c r="D27" s="320" t="n">
-        <f aca="false">F13</f>
-        <v>10.1016</v>
-      </c>
-      <c r="E27" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G62</f>
-        <v>0.1</v>
-      </c>
-      <c r="F27" s="320" t="n">
-        <f aca="false">D27*E27</f>
-        <v>1.01016</v>
-      </c>
-      <c r="G27" s="271" t="n">
-        <f aca="false">F27*SUMIF($B$68:$B$93,B27,$F$68:$F$93)</f>
-        <v>8.08128</v>
-      </c>
-      <c r="H27" s="313" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="317"/>
-      <c r="B28" s="310" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C28" s="314"/>
-      <c r="D28" s="314"/>
-      <c r="E28" s="314"/>
-      <c r="F28" s="314"/>
-      <c r="G28" s="298" t="n">
-        <f aca="false">SUM(G22:G27)</f>
-        <v>98.55019944</v>
-      </c>
-      <c r="H28" s="314"/>
-    </row>
-    <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="312" t="s">
-        <v>1010</v>
-      </c>
-      <c r="B29" s="310" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C29" s="310"/>
-      <c r="D29" s="310"/>
-      <c r="E29" s="310"/>
-      <c r="F29" s="310"/>
-      <c r="G29" s="310"/>
-      <c r="H29" s="310"/>
-    </row>
-    <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="317"/>
-      <c r="B30" s="314" t="s">
-        <v>802</v>
-      </c>
-      <c r="C30" s="315" t="s">
-        <v>803</v>
-      </c>
-      <c r="D30" s="320" t="n">
-        <f aca="false">F15</f>
-        <v>0.036992</v>
-      </c>
-      <c r="E30" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G28</f>
-        <v>9.73</v>
-      </c>
-      <c r="F30" s="320" t="n">
-        <f aca="false">D30*E30</f>
-        <v>0.35993216</v>
-      </c>
-      <c r="G30" s="271" t="n">
-        <f aca="false">F30*SUMIF($B$68:$B$93,B30,$F$68:$F$93)</f>
-        <v>11.1327017088</v>
-      </c>
-      <c r="H30" s="313" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="317"/>
-      <c r="B31" s="314" t="s">
-        <v>804</v>
-      </c>
-      <c r="C31" s="315" t="s">
-        <v>185</v>
-      </c>
-      <c r="D31" s="320" t="n">
-        <f aca="false">F15</f>
-        <v>0.036992</v>
-      </c>
-      <c r="E31" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G29</f>
-        <v>0.52</v>
-      </c>
-      <c r="F31" s="320" t="n">
-        <f aca="false">D31*E31</f>
-        <v>0.01923584</v>
-      </c>
-      <c r="G31" s="271" t="n">
-        <f aca="false">F31*SUMIF($B$68:$B$93,B31,$F$68:$F$93)</f>
-        <v>0.7825139712</v>
-      </c>
-      <c r="H31" s="313" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="317"/>
-      <c r="B32" s="314" t="s">
-        <v>805</v>
-      </c>
-      <c r="C32" s="315" t="s">
-        <v>185</v>
-      </c>
-      <c r="D32" s="320" t="n">
-        <f aca="false">F15</f>
-        <v>0.036992</v>
-      </c>
-      <c r="E32" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G30</f>
-        <v>0.53</v>
-      </c>
-      <c r="F32" s="320" t="n">
-        <f aca="false">D32*E32</f>
-        <v>0.01960576</v>
-      </c>
-      <c r="G32" s="271" t="n">
-        <f aca="false">F32*SUMIF($B$68:$B$93,B32,$F$68:$F$93)</f>
-        <v>1.9937097344</v>
-      </c>
-      <c r="H32" s="313" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="317"/>
-      <c r="B33" s="314" t="s">
-        <v>806</v>
-      </c>
-      <c r="C33" s="315" t="s">
-        <v>185</v>
-      </c>
-      <c r="D33" s="320" t="n">
-        <f aca="false">F15</f>
-        <v>0.036992</v>
-      </c>
-      <c r="E33" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G31</f>
-        <v>0.186</v>
-      </c>
-      <c r="F33" s="320" t="n">
-        <f aca="false">D33*E33</f>
-        <v>0.006880512</v>
-      </c>
-      <c r="G33" s="271" t="n">
-        <f aca="false">F33*SUMIF($B$68:$B$93,B33,$F$68:$F$93)</f>
-        <v>0.05731466496</v>
-      </c>
-      <c r="H33" s="313" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="317"/>
-      <c r="B34" s="314" t="s">
-        <v>807</v>
-      </c>
-      <c r="C34" s="315" t="s">
-        <v>808</v>
-      </c>
-      <c r="D34" s="320" t="n">
-        <f aca="false">F15</f>
-        <v>0.036992</v>
-      </c>
-      <c r="E34" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G32</f>
-        <v>0.8</v>
-      </c>
-      <c r="F34" s="320" t="n">
-        <f aca="false">D34*E34</f>
-        <v>0.0295936</v>
-      </c>
-      <c r="G34" s="271" t="n">
-        <f aca="false">F34*SUMIF($B$68:$B$93,B34,$F$68:$F$93)</f>
-        <v>0.376134656</v>
-      </c>
-      <c r="H34" s="313" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="317"/>
-      <c r="B35" s="314" t="s">
-        <v>809</v>
-      </c>
-      <c r="C35" s="315" t="s">
-        <v>808</v>
-      </c>
-      <c r="D35" s="320" t="n">
-        <f aca="false">F15</f>
-        <v>0.036992</v>
-      </c>
-      <c r="E35" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G33</f>
-        <v>0.8</v>
-      </c>
-      <c r="F35" s="320" t="n">
-        <f aca="false">D35*E35</f>
-        <v>0.0295936</v>
-      </c>
-      <c r="G35" s="271" t="n">
-        <f aca="false">F35*SUMIF($B$68:$B$93,B35,$F$68:$F$93)</f>
-        <v>0.326121472</v>
-      </c>
-      <c r="H35" s="313" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="317"/>
-      <c r="B36" s="314" t="s">
-        <v>810</v>
-      </c>
-      <c r="C36" s="315" t="s">
-        <v>811</v>
-      </c>
-      <c r="D36" s="320" t="n">
-        <f aca="false">F15</f>
-        <v>0.036992</v>
-      </c>
-      <c r="E36" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G34</f>
-        <v>0.8</v>
-      </c>
-      <c r="F36" s="320" t="n">
-        <f aca="false">D36*E36</f>
-        <v>0.0295936</v>
-      </c>
-      <c r="G36" s="271" t="n">
-        <f aca="false">F36*SUMIF($B$68:$B$93,B36,$F$68:$F$93)</f>
-        <v>0.85673472</v>
-      </c>
-      <c r="H36" s="313" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="317"/>
-      <c r="B37" s="314" t="s">
-        <v>812</v>
-      </c>
-      <c r="C37" s="315" t="s">
-        <v>811</v>
-      </c>
-      <c r="D37" s="320" t="n">
-        <f aca="false">F15</f>
-        <v>0.036992</v>
-      </c>
-      <c r="E37" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G35</f>
-        <v>0.8</v>
-      </c>
-      <c r="F37" s="320" t="n">
-        <f aca="false">D37*E37</f>
-        <v>0.0295936</v>
-      </c>
-      <c r="G37" s="271" t="n">
-        <f aca="false">F37*SUMIF($B$68:$B$93,B37,$F$68:$F$93)</f>
-        <v>0.671182848</v>
-      </c>
-      <c r="H37" s="313" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="317"/>
-      <c r="B38" s="314" t="s">
-        <v>813</v>
-      </c>
-      <c r="C38" s="315" t="s">
-        <v>811</v>
-      </c>
-      <c r="D38" s="320" t="n">
-        <f aca="false">F15</f>
-        <v>0.036992</v>
-      </c>
-      <c r="E38" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G36</f>
-        <v>6.4</v>
-      </c>
-      <c r="F38" s="320" t="n">
-        <f aca="false">D38*E38</f>
-        <v>0.2367488</v>
-      </c>
-      <c r="G38" s="271" t="n">
-        <f aca="false">F38*SUMIF($B$68:$B$93,B38,$F$68:$F$93)</f>
-        <v>4.862820352</v>
-      </c>
-      <c r="H38" s="313" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="317"/>
-      <c r="B39" s="310" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C39" s="314"/>
-      <c r="D39" s="314"/>
-      <c r="E39" s="314"/>
-      <c r="F39" s="314"/>
-      <c r="G39" s="298" t="n">
-        <f aca="false">SUM(G30:G38)</f>
-        <v>21.05923412736</v>
-      </c>
-      <c r="H39" s="314"/>
-    </row>
-    <row r="40" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="312" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B40" s="310" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C40" s="310"/>
-      <c r="D40" s="310"/>
-      <c r="E40" s="310"/>
-      <c r="F40" s="310"/>
-      <c r="G40" s="310"/>
-      <c r="H40" s="310"/>
-    </row>
-    <row r="41" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="317"/>
-      <c r="B41" s="314" t="s">
-        <v>817</v>
-      </c>
-      <c r="C41" s="315" t="s">
-        <v>818</v>
-      </c>
-      <c r="D41" s="320" t="n">
-        <f aca="false">F14</f>
-        <v>1.0</v>
-      </c>
-      <c r="E41" s="321" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="F41" s="320" t="n">
-        <f aca="false">D41*E41</f>
-        <v>1.15</v>
-      </c>
-      <c r="G41" s="271" t="n">
-        <f aca="false">F41*SUMIF($B$68:$B$93,B41,$F$68:$F$93)</f>
-        <v>5.0715</v>
-      </c>
-      <c r="H41" s="313" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="317"/>
-      <c r="B42" s="310" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C42" s="314"/>
-      <c r="D42" s="314"/>
-      <c r="E42" s="314"/>
-      <c r="F42" s="314"/>
-      <c r="G42" s="298" t="n">
-        <f aca="false">SUM(G41:G41)</f>
-        <v>5.0715</v>
-      </c>
-      <c r="H42" s="314"/>
-    </row>
-    <row r="43" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="312" t="s">
-        <v>1019</v>
-      </c>
-      <c r="B43" s="310" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C43" s="310"/>
-      <c r="D43" s="310"/>
-      <c r="E43" s="310"/>
-      <c r="F43" s="310"/>
-      <c r="G43" s="310"/>
-      <c r="H43" s="310"/>
-    </row>
-    <row r="44" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="317"/>
-      <c r="B44" s="314" t="s">
-        <v>1021</v>
-      </c>
-      <c r="C44" s="315" t="s">
-        <v>50</v>
-      </c>
-      <c r="D44" s="320" t="n">
-        <f aca="false">F16</f>
-        <v>17.3376</v>
-      </c>
-      <c r="E44" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G42</f>
-        <v>1.05</v>
-      </c>
-      <c r="F44" s="320" t="n">
-        <f aca="false">D44*E44</f>
-        <v>18.20448</v>
-      </c>
-      <c r="G44" s="271" t="n">
-        <f aca="false">F44*SUMIF($B$68:$B$93,B44,$F$68:$F$93)</f>
-        <v>62.6234112</v>
-      </c>
-      <c r="H44" s="313" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="317"/>
-      <c r="B45" s="314" t="s">
-        <v>823</v>
-      </c>
-      <c r="C45" s="315" t="s">
-        <v>50</v>
-      </c>
-      <c r="D45" s="320" t="n">
-        <f aca="false">F16</f>
-        <v>17.3376</v>
-      </c>
-      <c r="E45" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G43</f>
-        <v>0.06</v>
-      </c>
-      <c r="F45" s="320" t="n">
-        <f aca="false">D45*E45</f>
-        <v>1.040256</v>
-      </c>
-      <c r="G45" s="271" t="n">
-        <f aca="false">F45*SUMIF($B$68:$B$93,B45,$F$68:$F$93)</f>
-        <v>5.28450048</v>
-      </c>
-      <c r="H45" s="313" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="317"/>
-      <c r="B46" s="314" t="s">
-        <v>810</v>
-      </c>
-      <c r="C46" s="315" t="s">
-        <v>811</v>
-      </c>
-      <c r="D46" s="320" t="n">
-        <f aca="false">F16</f>
-        <v>17.3376</v>
-      </c>
-      <c r="E46" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G44</f>
-        <v>0.032</v>
-      </c>
-      <c r="F46" s="320" t="n">
-        <f aca="false">D46*E46</f>
-        <v>0.5548032</v>
-      </c>
-      <c r="G46" s="271" t="n">
-        <f aca="false">F46*SUMIF($B$68:$B$93,B46,$F$68:$F$93)</f>
-        <v>16.06155264</v>
-      </c>
-      <c r="H46" s="313" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="317"/>
-      <c r="B47" s="314" t="s">
-        <v>812</v>
-      </c>
-      <c r="C47" s="315" t="s">
-        <v>811</v>
-      </c>
-      <c r="D47" s="320" t="n">
-        <f aca="false">F16</f>
-        <v>17.3376</v>
-      </c>
-      <c r="E47" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G45</f>
-        <v>0.032</v>
-      </c>
-      <c r="F47" s="320" t="n">
-        <f aca="false">D47*E47</f>
-        <v>0.5548032</v>
-      </c>
-      <c r="G47" s="271" t="n">
-        <f aca="false">F47*SUMIF($B$68:$B$93,B47,$F$68:$F$93)</f>
-        <v>12.582936576</v>
-      </c>
-      <c r="H47" s="313" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="317"/>
-      <c r="B48" s="310" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C48" s="314"/>
-      <c r="D48" s="314"/>
-      <c r="E48" s="314"/>
-      <c r="F48" s="314"/>
-      <c r="G48" s="298" t="n">
-        <f aca="false">SUM(G44:G47)</f>
-        <v>96.552400896</v>
-      </c>
-      <c r="H48" s="314"/>
-    </row>
-    <row r="49" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="312" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B49" s="310" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C49" s="310"/>
-      <c r="D49" s="310"/>
-      <c r="E49" s="310"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-    </row>
-    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="317"/>
-      <c r="B50" s="314" t="s">
-        <v>838</v>
-      </c>
-      <c r="C50" s="315" t="s">
-        <v>839</v>
-      </c>
-      <c r="D50" s="320" t="n">
-        <f aca="false">F17</f>
-        <v>0.83904</v>
-      </c>
-      <c r="E50" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G64</f>
-        <v>0.08</v>
-      </c>
-      <c r="F50" s="320" t="n">
-        <f aca="false">D50*E50</f>
-        <v>0.0671232</v>
-      </c>
-      <c r="G50" s="271" t="n">
-        <f aca="false">F50*SUMIF($B$68:$B$93,B50,$F$68:$F$93)</f>
-        <v>3.015174144</v>
-      </c>
-      <c r="H50" s="313" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="317"/>
-      <c r="B51" s="314" t="s">
-        <v>840</v>
-      </c>
-      <c r="C51" s="315" t="s">
-        <v>839</v>
-      </c>
-      <c r="D51" s="320" t="n">
-        <f aca="false">F17</f>
-        <v>0.83904</v>
-      </c>
-      <c r="E51" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G65</f>
-        <v>0.08</v>
-      </c>
-      <c r="F51" s="320" t="n">
-        <f aca="false">D51*E51</f>
-        <v>0.0671232</v>
-      </c>
-      <c r="G51" s="271" t="n">
-        <f aca="false">F51*SUMIF($B$68:$B$93,B51,$F$68:$F$93)</f>
-        <v>3.242721792</v>
-      </c>
-      <c r="H51" s="313" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="317"/>
-      <c r="B52" s="314" t="s">
-        <v>902</v>
-      </c>
-      <c r="C52" s="315" t="s">
-        <v>60</v>
-      </c>
-      <c r="D52" s="320" t="n">
-        <f aca="false">F17</f>
-        <v>0.83904</v>
-      </c>
-      <c r="E52" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G66</f>
-        <v>0.25</v>
-      </c>
-      <c r="F52" s="320" t="n">
-        <f aca="false">D52*E52</f>
-        <v>0.20976</v>
-      </c>
-      <c r="G52" s="271" t="n">
-        <f aca="false">F52*SUMIF($B$68:$B$93,B52,$F$68:$F$93)</f>
-        <v>0.4446912</v>
-      </c>
-      <c r="H52" s="313" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="317"/>
-      <c r="B53" s="314" t="s">
-        <v>903</v>
-      </c>
-      <c r="C53" s="315" t="s">
-        <v>839</v>
-      </c>
-      <c r="D53" s="320" t="n">
-        <f aca="false">F17</f>
-        <v>0.83904</v>
-      </c>
-      <c r="E53" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G67</f>
-        <v>0.024</v>
-      </c>
-      <c r="F53" s="320" t="n">
-        <f aca="false">D53*E53</f>
-        <v>0.02013696</v>
-      </c>
-      <c r="G53" s="271" t="n">
-        <f aca="false">F53*SUMIF($B$68:$B$93,B53,$F$68:$F$93)</f>
-        <v>0.717882624</v>
-      </c>
-      <c r="H53" s="313" t="s">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="317"/>
-      <c r="B54" s="314" t="s">
-        <v>810</v>
-      </c>
-      <c r="C54" s="315" t="s">
-        <v>811</v>
-      </c>
-      <c r="D54" s="320" t="n">
-        <f aca="false">F17</f>
-        <v>0.83904</v>
-      </c>
-      <c r="E54" s="320" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G68</f>
-        <v>0.4</v>
-      </c>
-      <c r="F54" s="320" t="n">
-        <f aca="false">D54*E54</f>
-        <v>0.335616</v>
-      </c>
-      <c r="G54" s="271" t="n">
-        <f aca="false">F54*SUMIF($B$68:$B$93,B54,$F$68:$F$93)</f>
-        <v>9.7160832</v>
-      </c>
-      <c r="H54" s="313" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="317"/>
-      <c r="B55" s="310" t="s">
-        <v>1028</v>
-      </c>
-      <c r="C55" s="314"/>
-      <c r="D55" s="314"/>
-      <c r="E55" s="314"/>
-      <c r="F55" s="314"/>
-      <c r="G55" s="298" t="n">
-        <f aca="false">SUM(G50:G54)</f>
-        <v>17.13655296</v>
-      </c>
-      <c r="H55" s="314"/>
-    </row>
-    <row r="56" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="312" t="s">
-        <v>1029</v>
-      </c>
-      <c r="B56" s="310" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C56" s="310"/>
-      <c r="D56" s="310"/>
-      <c r="E56" s="310"/>
-      <c r="F56" s="310"/>
-      <c r="G56" s="310"/>
-      <c r="H56" s="310"/>
-    </row>
-    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="317"/>
-      <c r="B57" s="314" t="s">
-        <v>810</v>
-      </c>
-      <c r="C57" s="315" t="s">
-        <v>811</v>
-      </c>
-      <c r="D57" s="320" t="n">
-        <f aca="false">F14</f>
-        <v>1.0</v>
-      </c>
-      <c r="E57" s="321" t="n">
-        <v>1</v>
-      </c>
-      <c r="F57" s="320" t="n">
-        <f aca="false">D57*E57</f>
-        <v>1.0</v>
-      </c>
-      <c r="G57" s="271" t="n">
-        <f aca="false">F57*SUMIF($B$68:$B$93,B57,$F$68:$F$93)</f>
-        <v>28.95</v>
-      </c>
-      <c r="H57" s="313" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="317"/>
-      <c r="B58" s="314" t="s">
-        <v>813</v>
-      </c>
-      <c r="C58" s="315" t="s">
-        <v>811</v>
-      </c>
-      <c r="D58" s="320" t="n">
-        <f aca="false">F14</f>
-        <v>1.0</v>
-      </c>
-      <c r="E58" s="321" t="n">
-        <v>1</v>
-      </c>
-      <c r="F58" s="320" t="n">
-        <f aca="false">D58*E58</f>
-        <v>1.0</v>
-      </c>
-      <c r="G58" s="271" t="n">
-        <f aca="false">F58*SUMIF($B$68:$B$93,B58,$F$68:$F$93)</f>
-        <v>20.54</v>
-      </c>
-      <c r="H58" s="313" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="317"/>
-      <c r="B59" s="310" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C59" s="314"/>
-      <c r="D59" s="314"/>
-      <c r="E59" s="314"/>
-      <c r="F59" s="314"/>
-      <c r="G59" s="298" t="n">
-        <f aca="false">SUM(G57:G58)</f>
-        <v>49.49</v>
-      </c>
-      <c r="H59" s="314"/>
-    </row>
-    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="314"/>
-      <c r="B60" s="310" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C60" s="314"/>
-      <c r="D60" s="314"/>
-      <c r="E60" s="314"/>
-      <c r="F60" s="314"/>
-      <c r="G60" s="298" t="n">
-        <f aca="false">+G28+G39+G42+G48+G55+G59</f>
-        <v>287.85988742336</v>
-      </c>
-      <c r="H60" s="314"/>
-    </row>
-    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="310" t="s">
-        <v>1034</v>
-      </c>
-      <c r="B61" s="310"/>
-      <c r="C61" s="310"/>
-      <c r="D61" s="310"/>
-      <c r="E61" s="310"/>
-      <c r="F61" s="310"/>
-      <c r="G61" s="310"/>
-      <c r="H61" s="310"/>
-    </row>
-    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="310" t="s">
-        <v>1035</v>
-      </c>
-      <c r="B62" s="310"/>
-      <c r="C62" s="314" t="s">
-        <v>1036</v>
-      </c>
-      <c r="D62" s="314"/>
-      <c r="E62" s="314"/>
-      <c r="F62" s="314"/>
-      <c r="G62" s="314"/>
-      <c r="H62" s="314"/>
-    </row>
-    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="310" t="s">
-        <v>1037</v>
-      </c>
-      <c r="B63" s="310"/>
-      <c r="C63" s="314" t="s">
-        <v>1073</v>
-      </c>
-      <c r="D63" s="314"/>
-      <c r="E63" s="314"/>
-      <c r="F63" s="314"/>
-      <c r="G63" s="314"/>
-      <c r="H63" s="314"/>
-    </row>
-    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="310" t="s">
-        <v>490</v>
-      </c>
-      <c r="B64" s="310"/>
-      <c r="C64" s="314" t="s">
-        <v>60</v>
-      </c>
-      <c r="D64" s="314"/>
-      <c r="E64" s="314"/>
-      <c r="F64" s="314"/>
-      <c r="G64" s="314"/>
-      <c r="H64" s="314"/>
-    </row>
-    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="310" t="s">
-        <v>1039</v>
-      </c>
-      <c r="B65" s="310"/>
-      <c r="C65" s="271" t="n">
-        <f aca="false">+E11</f>
-        <v>11.0</v>
-      </c>
-      <c r="D65" s="271"/>
-      <c r="E65" s="271"/>
-      <c r="F65" s="271"/>
-      <c r="G65" s="271"/>
-      <c r="H65" s="271"/>
-    </row>
-    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="310" t="s">
-        <v>1040</v>
-      </c>
-      <c r="B66" s="310"/>
-      <c r="C66" s="271" t="n">
-        <f aca="false">8/E69</f>
-        <v>2.73021440919798</v>
-      </c>
-      <c r="D66" s="271"/>
-      <c r="E66" s="271"/>
-      <c r="F66" s="271"/>
-      <c r="G66" s="271"/>
-      <c r="H66" s="271"/>
-    </row>
-    <row r="67" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="311" t="s">
-        <v>309</v>
-      </c>
-      <c r="B67" s="311" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C67" s="311" t="s">
-        <v>170</v>
-      </c>
-      <c r="D67" s="311" t="s">
-        <v>1042</v>
-      </c>
-      <c r="E67" s="311" t="s">
-        <v>973</v>
-      </c>
-      <c r="F67" s="311" t="s">
-        <v>1043</v>
-      </c>
-      <c r="G67" s="311" t="s">
-        <v>998</v>
-      </c>
-      <c r="H67" s="311" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="317"/>
-      <c r="B68" s="310" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C68" s="310"/>
-      <c r="D68" s="310"/>
-      <c r="E68" s="310"/>
-      <c r="F68" s="310"/>
-      <c r="G68" s="310"/>
-      <c r="H68" s="310"/>
-    </row>
-    <row r="69" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="312" t="n">
-        <v>1</v>
-      </c>
-      <c r="B69" s="314" t="s">
-        <v>810</v>
-      </c>
-      <c r="C69" s="315" t="s">
-        <v>811</v>
-      </c>
-      <c r="D69" s="320" t="n">
-        <f aca="false">E69*$C$66/8</f>
-        <v>1.0</v>
-      </c>
-      <c r="E69" s="320" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B69,$F$21:$F$59)</f>
-        <v>2.9301728</v>
-      </c>
-      <c r="F69" s="316" t="n">
+      <c r="E37" s="306" t="n">
+        <f aca="false">$D$12*$D$23+($D$15+$D$16+$D$17)*$D$25+$D$13*$D$26+$D$27</f>
+        <v>1.7472768</v>
+      </c>
+      <c r="F37" s="290" t="n">
         <f aca="false">'COSTO HORA HOMBRE 2026'!$G$11</f>
         <v>28.95</v>
       </c>
-      <c r="G69" s="271" t="n">
-        <f aca="false">E69*F69</f>
-        <v>84.82850256</v>
-      </c>
-      <c r="H69" s="313" t="s">
+      <c r="G37" s="290" t="n">
+        <f aca="false">E37*F37</f>
+        <v>50.58366336</v>
+      </c>
+      <c r="H37" s="149" t="s">
         <v>1046</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="312" t="n">
-        <v>2</v>
-      </c>
-      <c r="B70" s="314" t="s">
+    <row r="38" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="283" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B38" s="295" t="s">
         <v>812</v>
       </c>
-      <c r="C70" s="315" t="s">
+      <c r="C38" s="285" t="s">
         <v>811</v>
       </c>
-      <c r="D70" s="320" t="n">
-        <f aca="false">E70*$C$66/8</f>
-        <v>0.544185243955578</v>
-      </c>
-      <c r="E70" s="320" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B70,$F$21:$F$59)</f>
-        <v>1.5945568</v>
-      </c>
-      <c r="F70" s="316" t="n">
+      <c r="D38" s="306" t="n">
+        <f aca="false">E38*$C$34/8</f>
+        <v>0.427680834542071</v>
+      </c>
+      <c r="E38" s="306" t="n">
+        <f aca="false">$D$12*$D$23+($D$15+$D$16+$D$17)*$D$25+$D$13*$D$26</f>
+        <v>0.7472768</v>
+      </c>
+      <c r="F38" s="290" t="n">
         <f aca="false">'COSTO HORA HOMBRE 2026'!$G$12</f>
         <v>22.68</v>
       </c>
-      <c r="G70" s="271" t="n">
-        <f aca="false">E70*F70</f>
-        <v>36.164548224</v>
-      </c>
-      <c r="H70" s="313" t="s">
+      <c r="G38" s="290" t="n">
+        <f aca="false">E38*F38</f>
+        <v>16.948237824</v>
+      </c>
+      <c r="H38" s="149" t="s">
         <v>1046</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="312" t="n">
-        <v>3</v>
-      </c>
-      <c r="B71" s="314" t="s">
+    <row r="39" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="283" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B39" s="295" t="s">
         <v>813</v>
       </c>
-      <c r="C71" s="315" t="s">
+      <c r="C39" s="285" t="s">
         <v>811</v>
       </c>
-      <c r="D71" s="320" t="n">
-        <f aca="false">E71*$C$66/8</f>
-        <v>0.422073674289789</v>
-      </c>
-      <c r="E71" s="320" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B71,$F$21:$F$59)</f>
+      <c r="D39" s="306" t="n">
+        <f aca="false">E39*$C$34/8</f>
+        <v>0.707815041097095</v>
+      </c>
+      <c r="E39" s="306" t="n">
+        <f aca="false">$D$12*$D$24+$D$27</f>
         <v>1.2367488</v>
       </c>
-      <c r="F71" s="316" t="n">
+      <c r="F39" s="290" t="n">
         <f aca="false">'COSTO HORA HOMBRE 2026'!$G$13</f>
         <v>20.54</v>
       </c>
-      <c r="G71" s="271" t="n">
-        <f aca="false">E71*F71</f>
+      <c r="G39" s="290" t="n">
+        <f aca="false">E39*F39</f>
         <v>25.402820352</v>
       </c>
-      <c r="H71" s="313" t="s">
+      <c r="H39" s="149" t="s">
         <v>1046</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="317"/>
-      <c r="B72" s="310" t="s">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="21"/>
+      <c r="B40" s="294" t="s">
         <v>1047</v>
       </c>
-      <c r="C72" s="314"/>
-      <c r="D72" s="314"/>
-      <c r="E72" s="314"/>
-      <c r="F72" s="314"/>
-      <c r="G72" s="298" t="n">
-        <f aca="false">SUM(G69:G71)</f>
-        <v>146.395871136</v>
-      </c>
-      <c r="H72" s="314"/>
-    </row>
-    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="317"/>
-      <c r="B73" s="310" t="s">
+      <c r="C40" s="295"/>
+      <c r="D40" s="295"/>
+      <c r="E40" s="295"/>
+      <c r="F40" s="295"/>
+      <c r="G40" s="296" t="n">
+        <f aca="false">SUM(G37:G39)</f>
+        <v>92.934721536</v>
+      </c>
+      <c r="H40" s="295"/>
+    </row>
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="21"/>
+      <c r="B41" s="294" t="s">
         <v>1048</v>
       </c>
-      <c r="C73" s="310"/>
-      <c r="D73" s="310"/>
-      <c r="E73" s="310"/>
-      <c r="F73" s="310"/>
-      <c r="G73" s="310"/>
-      <c r="H73" s="310"/>
-    </row>
-    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="312" t="n">
-        <v>4</v>
-      </c>
-      <c r="B74" s="314" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C74" s="315" t="s">
+      <c r="C41" s="294"/>
+      <c r="D41" s="294"/>
+      <c r="E41" s="294"/>
+      <c r="F41" s="294"/>
+      <c r="G41" s="294"/>
+      <c r="H41" s="294"/>
+    </row>
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="283" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B42" s="295" t="s">
+        <v>802</v>
+      </c>
+      <c r="C42" s="285" t="s">
+        <v>803</v>
+      </c>
+      <c r="D42" s="295"/>
+      <c r="E42" s="306" t="n">
+        <f aca="false">$D$12*$D$19</f>
+        <v>0.35993216</v>
+      </c>
+      <c r="F42" s="289" t="n">
+        <v>30.93</v>
+      </c>
+      <c r="G42" s="290" t="n">
+        <f aca="false">E42*F42</f>
+        <v>11.1327017088</v>
+      </c>
+      <c r="H42" s="149" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="283" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B43" s="295" t="s">
+        <v>804</v>
+      </c>
+      <c r="C43" s="285" t="s">
+        <v>185</v>
+      </c>
+      <c r="D43" s="295"/>
+      <c r="E43" s="306" t="n">
+        <f aca="false">$D$12*$D$20</f>
+        <v>0.01923584</v>
+      </c>
+      <c r="F43" s="289" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="G43" s="290" t="n">
+        <f aca="false">E43*F43</f>
+        <v>0.7825139712</v>
+      </c>
+      <c r="H43" s="149" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="283" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B44" s="295" t="s">
+        <v>805</v>
+      </c>
+      <c r="C44" s="285" t="s">
+        <v>185</v>
+      </c>
+      <c r="D44" s="295"/>
+      <c r="E44" s="306" t="n">
+        <f aca="false">$D$12*$D$21</f>
+        <v>0.01960576</v>
+      </c>
+      <c r="F44" s="289" t="n">
+        <v>101.69</v>
+      </c>
+      <c r="G44" s="290" t="n">
+        <f aca="false">E44*F44</f>
+        <v>1.9937097344</v>
+      </c>
+      <c r="H44" s="149" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="283" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B45" s="295" t="s">
+        <v>806</v>
+      </c>
+      <c r="C45" s="285" t="s">
+        <v>185</v>
+      </c>
+      <c r="D45" s="295"/>
+      <c r="E45" s="306" t="n">
+        <f aca="false">$D$12*$D$22+0.01</f>
+        <v>0.016880512</v>
+      </c>
+      <c r="F45" s="289" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="G45" s="290" t="n">
+        <f aca="false">E45*F45</f>
+        <v>0.14061466496</v>
+      </c>
+      <c r="H45" s="149" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="283" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B46" s="295" t="s">
+        <v>817</v>
+      </c>
+      <c r="C46" s="285" t="s">
+        <v>818</v>
+      </c>
+      <c r="D46" s="295"/>
+      <c r="E46" s="306" t="n">
+        <f aca="false">$D$13*4.24/6+$D$14</f>
+        <v>1.30377066666667</v>
+      </c>
+      <c r="F46" s="289" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="G46" s="290" t="n">
+        <f aca="false">E46*F46</f>
+        <v>5.74962864</v>
+      </c>
+      <c r="H46" s="149" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="283" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B47" s="295" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C47" s="285" t="s">
         <v>50</v>
       </c>
-      <c r="D74" s="314"/>
-      <c r="E74" s="320" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B74,$F$21:$F$59)</f>
-        <v>10.60668</v>
-      </c>
-      <c r="F74" s="316" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="G74" s="271" t="n">
-        <f aca="false">E74*F74</f>
-        <v>32.6685744</v>
-      </c>
-      <c r="H74" s="313" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="312" t="n">
-        <v>5</v>
-      </c>
-      <c r="B75" s="314" t="s">
-        <v>1005</v>
-      </c>
-      <c r="C75" s="315" t="s">
+      <c r="D47" s="295"/>
+      <c r="E47" s="306" t="n">
+        <f aca="false">($D$15+$D$16)*(1+$D$18)</f>
+        <v>16.79328</v>
+      </c>
+      <c r="F47" s="289" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="G47" s="290" t="n">
+        <f aca="false">E47*F47</f>
+        <v>57.7688832</v>
+      </c>
+      <c r="H47" s="149" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="283" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B48" s="295" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C48" s="285" t="s">
         <v>50</v>
       </c>
-      <c r="D75" s="314"/>
-      <c r="E75" s="320" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B75,$F$21:$F$59)</f>
-        <v>0.303048</v>
-      </c>
-      <c r="F75" s="316" t="n">
-        <v>18.63</v>
-      </c>
-      <c r="G75" s="271" t="n">
-        <f aca="false">E75*F75</f>
-        <v>5.64578424</v>
-      </c>
-      <c r="H75" s="313" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="312" t="n">
-        <v>6</v>
-      </c>
-      <c r="B76" s="314" t="s">
-        <v>802</v>
-      </c>
-      <c r="C76" s="315" t="s">
-        <v>803</v>
-      </c>
-      <c r="D76" s="314"/>
-      <c r="E76" s="320" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B76,$F$21:$F$59)</f>
-        <v>0.35993216</v>
-      </c>
-      <c r="F76" s="316" t="n">
-        <v>30.93</v>
-      </c>
-      <c r="G76" s="271" t="n">
-        <f aca="false">E76*F76</f>
-        <v>11.1327017088</v>
-      </c>
-      <c r="H76" s="313" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="312" t="n">
-        <v>7</v>
-      </c>
-      <c r="B77" s="314" t="s">
-        <v>804</v>
-      </c>
-      <c r="C77" s="315" t="s">
-        <v>185</v>
-      </c>
-      <c r="D77" s="314"/>
-      <c r="E77" s="320" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B77,$F$21:$F$59)</f>
-        <v>0.01923584</v>
-      </c>
-      <c r="F77" s="316" t="n">
-        <v>40.68</v>
-      </c>
-      <c r="G77" s="271" t="n">
-        <f aca="false">E77*F77</f>
-        <v>0.7825139712</v>
-      </c>
-      <c r="H77" s="313" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="312" t="n">
-        <v>8</v>
-      </c>
-      <c r="B78" s="314" t="s">
-        <v>805</v>
-      </c>
-      <c r="C78" s="315" t="s">
-        <v>185</v>
-      </c>
-      <c r="D78" s="314"/>
-      <c r="E78" s="320" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B78,$F$21:$F$59)</f>
-        <v>0.01960576</v>
-      </c>
-      <c r="F78" s="316" t="n">
-        <v>101.69</v>
-      </c>
-      <c r="G78" s="271" t="n">
-        <f aca="false">E78*F78</f>
-        <v>1.9937097344</v>
-      </c>
-      <c r="H78" s="313" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="312" t="n">
-        <v>9</v>
-      </c>
-      <c r="B79" s="314" t="s">
-        <v>806</v>
-      </c>
-      <c r="C79" s="315" t="s">
-        <v>185</v>
-      </c>
-      <c r="D79" s="314"/>
-      <c r="E79" s="320" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B79,$F$21:$F$59)</f>
-        <v>0.006880512</v>
-      </c>
-      <c r="F79" s="316" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="G79" s="271" t="n">
-        <f aca="false">E79*F79</f>
-        <v>0.05731466496</v>
-      </c>
-      <c r="H79" s="313" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="312" t="n">
-        <v>10</v>
-      </c>
-      <c r="B80" s="314" t="s">
-        <v>817</v>
-      </c>
-      <c r="C80" s="315" t="s">
-        <v>818</v>
-      </c>
-      <c r="D80" s="314"/>
-      <c r="E80" s="320" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B80,$F$21:$F$59)</f>
-        <v>1.15</v>
-      </c>
-      <c r="F80" s="316" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="G80" s="271" t="n">
-        <f aca="false">E80*F80</f>
-        <v>5.0715</v>
-      </c>
-      <c r="H80" s="313" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="312" t="n">
-        <v>11</v>
-      </c>
-      <c r="B81" s="314" t="s">
-        <v>1021</v>
-      </c>
-      <c r="C81" s="315" t="s">
+      <c r="D48" s="295"/>
+      <c r="E48" s="306" t="n">
+        <f aca="false">$D$17*(1+$D$18)</f>
+        <v>1.0437</v>
+      </c>
+      <c r="F48" s="289" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="G48" s="290" t="n">
+        <f aca="false">E48*F48</f>
+        <v>3.590328</v>
+      </c>
+      <c r="H48" s="149" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="283" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B49" s="295" t="s">
+        <v>823</v>
+      </c>
+      <c r="C49" s="285" t="s">
         <v>50</v>
       </c>
-      <c r="D81" s="314"/>
-      <c r="E81" s="320" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B81,$F$21:$F$59)</f>
-        <v>18.20448</v>
-      </c>
-      <c r="F81" s="316" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="G81" s="271" t="n">
-        <f aca="false">E81*F81</f>
-        <v>62.6234112</v>
-      </c>
-      <c r="H81" s="313" t="s">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="312" t="n">
-        <v>12</v>
-      </c>
-      <c r="B82" s="314" t="s">
-        <v>823</v>
-      </c>
-      <c r="C82" s="315" t="s">
-        <v>50</v>
-      </c>
-      <c r="D82" s="314"/>
-      <c r="E82" s="320" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B82,$F$21:$F$59)</f>
-        <v>1.040256</v>
-      </c>
-      <c r="F82" s="316" t="n">
+      <c r="D49" s="295"/>
+      <c r="E49" s="306" t="n">
+        <f aca="false">($D$15+$D$16+$D$17)*0.06</f>
+        <v>1.019256</v>
+      </c>
+      <c r="F49" s="289" t="n">
         <v>5.08</v>
       </c>
-      <c r="G82" s="271" t="n">
-        <f aca="false">E82*F82</f>
-        <v>5.28450048</v>
-      </c>
-      <c r="H82" s="313" t="s">
+      <c r="G49" s="290" t="n">
+        <f aca="false">E49*F49</f>
+        <v>5.17782048</v>
+      </c>
+      <c r="H49" s="149" t="s">
         <v>1057</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="312" t="n">
-        <v>13</v>
-      </c>
-      <c r="B83" s="314" t="s">
-        <v>838</v>
-      </c>
-      <c r="C83" s="315" t="s">
-        <v>839</v>
-      </c>
-      <c r="D83" s="314"/>
-      <c r="E83" s="320" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B83,$F$21:$F$59)</f>
-        <v>0.0671232</v>
-      </c>
-      <c r="F83" s="316" t="n">
-        <v>44.92</v>
-      </c>
-      <c r="G83" s="271" t="n">
-        <f aca="false">E83*F83</f>
-        <v>3.015174144</v>
-      </c>
-      <c r="H83" s="313" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="312" t="n">
-        <v>14</v>
-      </c>
-      <c r="B84" s="314" t="s">
-        <v>840</v>
-      </c>
-      <c r="C84" s="315" t="s">
-        <v>839</v>
-      </c>
-      <c r="D84" s="314"/>
-      <c r="E84" s="320" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B84,$F$21:$F$59)</f>
-        <v>0.0671232</v>
-      </c>
-      <c r="F84" s="316" t="n">
-        <v>48.31</v>
-      </c>
-      <c r="G84" s="271" t="n">
-        <f aca="false">E84*F84</f>
-        <v>3.242721792</v>
-      </c>
-      <c r="H84" s="313" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="312" t="n">
-        <v>15</v>
-      </c>
-      <c r="B85" s="314" t="s">
-        <v>902</v>
-      </c>
-      <c r="C85" s="315" t="s">
-        <v>60</v>
-      </c>
-      <c r="D85" s="314"/>
-      <c r="E85" s="320" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B85,$F$21:$F$59)</f>
-        <v>0.20976</v>
-      </c>
-      <c r="F85" s="316" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="G85" s="271" t="n">
-        <f aca="false">E85*F85</f>
-        <v>0.4446912</v>
-      </c>
-      <c r="H85" s="313" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="312" t="n">
-        <v>16</v>
-      </c>
-      <c r="B86" s="314" t="s">
-        <v>903</v>
-      </c>
-      <c r="C86" s="315" t="s">
-        <v>839</v>
-      </c>
-      <c r="D86" s="314"/>
-      <c r="E86" s="320" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B86,$F$21:$F$59)</f>
-        <v>0.02013696</v>
-      </c>
-      <c r="F86" s="316" t="n">
-        <v>35.65</v>
-      </c>
-      <c r="G86" s="271" t="n">
-        <f aca="false">E86*F86</f>
-        <v>0.717882624</v>
-      </c>
-      <c r="H86" s="313" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="317"/>
-      <c r="B87" s="310" t="s">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="21"/>
+      <c r="B50" s="294" t="s">
         <v>1062</v>
       </c>
-      <c r="C87" s="314"/>
-      <c r="D87" s="314"/>
-      <c r="E87" s="314"/>
-      <c r="F87" s="314"/>
-      <c r="G87" s="298" t="n">
-        <f aca="false">SUM(G74:G86)</f>
-        <v>132.68048015936</v>
-      </c>
-      <c r="H87" s="314"/>
-    </row>
-    <row r="88" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="317"/>
-      <c r="B88" s="310" t="s">
+      <c r="C50" s="295"/>
+      <c r="D50" s="295"/>
+      <c r="E50" s="295"/>
+      <c r="F50" s="295"/>
+      <c r="G50" s="296" t="n">
+        <f aca="false">SUM(G42:G49)</f>
+        <v>86.33620039936</v>
+      </c>
+      <c r="H50" s="295"/>
+    </row>
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="21"/>
+      <c r="B51" s="294" t="s">
         <v>1063</v>
       </c>
-      <c r="C88" s="310"/>
-      <c r="D88" s="310"/>
-      <c r="E88" s="310"/>
-      <c r="F88" s="310"/>
-      <c r="G88" s="310"/>
-      <c r="H88" s="310"/>
-    </row>
-    <row r="89" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="312" t="n">
-        <v>17</v>
-      </c>
-      <c r="B89" s="314" t="s">
+      <c r="C51" s="294"/>
+      <c r="D51" s="294"/>
+      <c r="E51" s="294"/>
+      <c r="F51" s="294"/>
+      <c r="G51" s="294"/>
+      <c r="H51" s="294"/>
+    </row>
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="283" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B52" s="295" t="s">
         <v>827</v>
       </c>
-      <c r="C89" s="315" t="s">
+      <c r="C52" s="285" t="s">
         <v>828</v>
       </c>
-      <c r="D89" s="314"/>
-      <c r="E89" s="322" t="n">
+      <c r="D52" s="295"/>
+      <c r="E52" s="284" t="n">
         <v>0.03</v>
       </c>
-      <c r="F89" s="271" t="n">
-        <f aca="false">+G72</f>
-        <v>146.395871136</v>
-      </c>
-      <c r="G89" s="271" t="n">
-        <f aca="false">E89*F89</f>
-        <v>4.39187613408</v>
-      </c>
-      <c r="H89" s="313" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="312" t="n">
-        <v>18</v>
-      </c>
-      <c r="B90" s="314" t="s">
-        <v>807</v>
-      </c>
-      <c r="C90" s="315" t="s">
-        <v>808</v>
-      </c>
-      <c r="D90" s="320" t="n">
-        <f aca="false">E90*$C$66/8</f>
-        <v>0.0100996091425052</v>
-      </c>
-      <c r="E90" s="320" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B90,$F$21:$F$59)</f>
-        <v>0.0295936</v>
-      </c>
-      <c r="F90" s="316" t="n">
-        <v>12.71</v>
-      </c>
-      <c r="G90" s="271" t="n">
-        <f aca="false">E90*F90</f>
-        <v>0.376134656</v>
-      </c>
-      <c r="H90" s="313" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="312" t="n">
-        <v>19</v>
-      </c>
-      <c r="B91" s="314" t="s">
-        <v>809</v>
-      </c>
-      <c r="C91" s="315" t="s">
-        <v>808</v>
-      </c>
-      <c r="D91" s="320" t="n">
-        <f aca="false">E91*$C$66/8</f>
-        <v>0.0100996091425052</v>
-      </c>
-      <c r="E91" s="320" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B91,$F$21:$F$59)</f>
-        <v>0.0295936</v>
-      </c>
-      <c r="F91" s="316" t="n">
-        <v>11.02</v>
-      </c>
-      <c r="G91" s="271" t="n">
-        <f aca="false">E91*F91</f>
-        <v>0.326121472</v>
-      </c>
-      <c r="H91" s="313" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="312" t="n">
-        <v>20</v>
-      </c>
-      <c r="B92" s="314" t="s">
-        <v>1007</v>
-      </c>
-      <c r="C92" s="315" t="s">
-        <v>808</v>
-      </c>
-      <c r="D92" s="320" t="n">
-        <f aca="false">E92*$C$66/8</f>
-        <v>0.344744173449429</v>
-      </c>
-      <c r="E92" s="320" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B92,$F$21:$F$59)</f>
-        <v>1.01016</v>
-      </c>
-      <c r="F92" s="316" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="G92" s="271" t="n">
-        <f aca="false">E92*F92</f>
-        <v>8.08128</v>
-      </c>
-      <c r="H92" s="313" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="317"/>
-      <c r="B93" s="310" t="s">
+      <c r="F52" s="290" t="n">
+        <f aca="false">+G40</f>
+        <v>92.934721536</v>
+      </c>
+      <c r="G52" s="290" t="n">
+        <f aca="false">E52*F52</f>
+        <v>2.78804164608</v>
+      </c>
+      <c r="H52" s="149" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="21"/>
+      <c r="B53" s="294" t="s">
         <v>1068</v>
       </c>
-      <c r="C93" s="314"/>
-      <c r="D93" s="314"/>
-      <c r="E93" s="314"/>
-      <c r="F93" s="314"/>
-      <c r="G93" s="298" t="n">
-        <f aca="false">SUM(G89:G92)</f>
-        <v>13.17541226208</v>
-      </c>
-      <c r="H93" s="314"/>
-    </row>
-    <row r="94" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="310" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B94" s="310"/>
-      <c r="C94" s="310"/>
-      <c r="D94" s="310"/>
-      <c r="E94" s="310"/>
-      <c r="F94" s="310"/>
-      <c r="G94" s="298" t="n">
-        <f aca="false">+G72+G87+G93</f>
-        <v>292.25176355744</v>
-      </c>
-      <c r="H94" s="314"/>
-    </row>
-    <row r="95" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="310" t="s">
-        <v>1070</v>
-      </c>
-      <c r="B95" s="310"/>
-      <c r="C95" s="310"/>
-      <c r="D95" s="310"/>
-      <c r="E95" s="310"/>
-      <c r="F95" s="310"/>
-      <c r="G95" s="298" t="n">
-        <f aca="false">G94*C65</f>
-        <v>3214.76939913184</v>
-      </c>
-      <c r="H95" s="314"/>
-    </row>
-    <row r="96" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="314" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B96" s="314"/>
-      <c r="C96" s="314"/>
-      <c r="D96" s="314"/>
-      <c r="E96" s="314"/>
-      <c r="F96" s="314"/>
-      <c r="G96" s="312" t="str">
-        <f aca="false">IF(ABS(G60+G89-G94)&lt;0.005,"CONFORME","REVISAR")</f>
-        <v>CONFORME</v>
-      </c>
-      <c r="H96" s="314"/>
+      <c r="C53" s="295"/>
+      <c r="D53" s="295"/>
+      <c r="E53" s="295"/>
+      <c r="F53" s="295"/>
+      <c r="G53" s="296" t="n">
+        <f aca="false">SUM(G52:G52)</f>
+        <v>2.78804164608</v>
+      </c>
+      <c r="H53" s="295"/>
+    </row>
+    <row r="54" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="294" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B54" s="294"/>
+      <c r="C54" s="294"/>
+      <c r="D54" s="294"/>
+      <c r="E54" s="294"/>
+      <c r="F54" s="294"/>
+      <c r="G54" s="296" t="n">
+        <f aca="false">+G40+G50+G53</f>
+        <v>182.05896358144</v>
+      </c>
+      <c r="H54" s="295"/>
+    </row>
+    <row r="55" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="294" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B55" s="294"/>
+      <c r="C55" s="294"/>
+      <c r="D55" s="294"/>
+      <c r="E55" s="294"/>
+      <c r="F55" s="294"/>
+      <c r="G55" s="296" t="n">
+        <f aca="false">G54*C33</f>
+        <v>2002.64859939584</v>
+      </c>
+      <c r="H55" s="295"/>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="27">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:H2"/>
@@ -25445,30 +24591,22 @@
     <mergeCell ref="C5:H5"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="B43:H43"/>
-    <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B56:H56"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="C62:H62"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="C63:H63"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="C64:H64"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="C65:H65"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="C66:H66"/>
-    <mergeCell ref="B68:H68"/>
-    <mergeCell ref="B73:H73"/>
-    <mergeCell ref="B88:H88"/>
-    <mergeCell ref="A94:F94"/>
-    <mergeCell ref="A95:F95"/>
-    <mergeCell ref="A96:F96"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="B51:H51"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A55:F55"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -27496,7 +26634,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="318" width="6"/>
@@ -27506,16 +26644,17 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="318" width="40"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="306" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B1" s="306"/>
-      <c r="C1" s="306"/>
-      <c r="D1" s="306"/>
-      <c r="E1" s="306"/>
-      <c r="F1" s="306"/>
-      <c r="G1" s="306"/>
+    <row r="1" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="277" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B1" s="277"/>
+      <c r="C1" s="277"/>
+      <c r="D1" s="277"/>
+      <c r="E1" s="277"/>
+      <c r="F1" s="277"/>
+      <c r="G1" s="277"/>
+      <c r="H1" s="277"/>
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="307" t="s">
@@ -27573,860 +26712,763 @@
       <c r="F5" s="266"/>
       <c r="G5" s="266"/>
     </row>
-    <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="309" t="s">
-        <v>1144</v>
-      </c>
-      <c r="B7" s="309"/>
-      <c r="C7" s="309"/>
-      <c r="D7" s="309"/>
-      <c r="E7" s="309"/>
-      <c r="F7" s="309"/>
-      <c r="G7" s="309"/>
+    <row r="7" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="281" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B7" s="281"/>
+      <c r="C7" s="281"/>
+      <c r="D7" s="281"/>
+      <c r="E7" s="281"/>
+      <c r="F7" s="281"/>
+      <c r="G7" s="281"/>
+      <c r="H7" s="281"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="310" t="s">
+      <c r="A9" s="294" t="s">
         <v>1145</v>
       </c>
-      <c r="B9" s="310"/>
-      <c r="C9" s="310"/>
-      <c r="D9" s="310"/>
-      <c r="E9" s="310"/>
-      <c r="F9" s="310"/>
-      <c r="G9" s="310"/>
-    </row>
-    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="311" t="s">
+      <c r="B9" s="294"/>
+      <c r="C9" s="294"/>
+      <c r="D9" s="294"/>
+      <c r="E9" s="294"/>
+      <c r="F9" s="294"/>
+      <c r="G9" s="294"/>
+      <c r="H9" s="294"/>
+    </row>
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="282" t="s">
         <v>309</v>
       </c>
-      <c r="B10" s="311" t="s">
+      <c r="B10" s="282" t="s">
         <v>723</v>
       </c>
-      <c r="C10" s="311" t="s">
+      <c r="C10" s="282" t="s">
         <v>724</v>
       </c>
-      <c r="D10" s="311" t="s">
+      <c r="D10" s="282" t="s">
         <v>725</v>
       </c>
-      <c r="E10" s="311"/>
-      <c r="F10" s="311" t="s">
+      <c r="E10" s="282"/>
+      <c r="F10" s="282" t="s">
         <v>1146</v>
       </c>
-      <c r="G10" s="311" t="s">
+      <c r="G10" s="282" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="312" t="n">
+      <c r="H10" s="282"/>
+    </row>
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="283" t="n">
         <v>1.0</v>
       </c>
-      <c r="B11" s="312" t="str">
+      <c r="B11" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!B10</f>
         <v>RV-01</v>
       </c>
-      <c r="C11" s="312" t="str">
+      <c r="C11" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!C10</f>
         <v>0+007.01</v>
       </c>
-      <c r="D11" s="313" t="str">
+      <c r="D11" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!D10</f>
         <v>Registro en la losa del colector; empalme cuneta Eje 09</v>
       </c>
-      <c r="E11" s="313"/>
-      <c r="F11" s="271" t="n">
+      <c r="E11" s="295"/>
+      <c r="F11" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E10</f>
         <v>1.0</v>
       </c>
-      <c r="G11" s="312" t="str">
+      <c r="G11" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F10</f>
         <v>DP-01, DP-06B</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="312" t="n">
+      <c r="H11" s="295"/>
+    </row>
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="283" t="n">
         <v>2.0</v>
       </c>
-      <c r="B12" s="312" t="str">
+      <c r="B12" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!B11</f>
         <v>RV-02</v>
       </c>
-      <c r="C12" s="312" t="str">
+      <c r="C12" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!C11</f>
         <v>0+013.52</v>
       </c>
-      <c r="D12" s="313" t="str">
+      <c r="D12" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!D11</f>
         <v>Registro en la losa del colector; limpieza</v>
       </c>
-      <c r="E12" s="313"/>
-      <c r="F12" s="271" t="n">
+      <c r="E12" s="295"/>
+      <c r="F12" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E11</f>
         <v>1.0</v>
       </c>
-      <c r="G12" s="312" t="str">
+      <c r="G12" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F11</f>
         <v>DP-01, DP-06B</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="312" t="n">
+      <c r="H12" s="295"/>
+    </row>
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="283" t="n">
         <v>3.0</v>
       </c>
-      <c r="B13" s="312" t="str">
+      <c r="B13" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!B12</f>
         <v>RV-03</v>
       </c>
-      <c r="C13" s="312" t="str">
+      <c r="C13" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!C12</f>
         <v>0+020.02</v>
       </c>
-      <c r="D13" s="313" t="str">
+      <c r="D13" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!D12</f>
         <v>Registro en la losa del colector; empalme cuneta Eje 08</v>
       </c>
-      <c r="E13" s="313"/>
-      <c r="F13" s="271" t="n">
+      <c r="E13" s="295"/>
+      <c r="F13" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E12</f>
         <v>1.0</v>
       </c>
-      <c r="G13" s="312" t="str">
+      <c r="G13" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F12</f>
         <v>DP-01, DP-06B</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="312" t="n">
+      <c r="H13" s="295"/>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="283" t="n">
         <v>4.0</v>
       </c>
-      <c r="B14" s="312" t="str">
+      <c r="B14" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!B13</f>
         <v>RV-04</v>
       </c>
-      <c r="C14" s="312" t="str">
+      <c r="C14" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!C13</f>
         <v>0+028.72</v>
       </c>
-      <c r="D14" s="313" t="str">
+      <c r="D14" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!D13</f>
         <v>Registro en la losa del colector; limpieza</v>
       </c>
-      <c r="E14" s="313"/>
-      <c r="F14" s="271" t="n">
+      <c r="E14" s="295"/>
+      <c r="F14" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E13</f>
         <v>1.0</v>
       </c>
-      <c r="G14" s="312" t="str">
+      <c r="G14" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F13</f>
         <v>DP-01, DP-06B</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="312" t="n">
+      <c r="H14" s="295"/>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="283" t="n">
         <v>5.0</v>
       </c>
-      <c r="B15" s="312" t="str">
+      <c r="B15" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!B14</f>
         <v>RV-05</v>
       </c>
-      <c r="C15" s="312" t="str">
+      <c r="C15" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!C14</f>
         <v>0+037.41</v>
       </c>
-      <c r="D15" s="313" t="str">
+      <c r="D15" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!D14</f>
         <v>Registro en la losa del colector; limpieza</v>
       </c>
-      <c r="E15" s="313"/>
-      <c r="F15" s="271" t="n">
+      <c r="E15" s="295"/>
+      <c r="F15" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E14</f>
         <v>1.0</v>
       </c>
-      <c r="G15" s="312" t="str">
+      <c r="G15" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F14</f>
         <v>DP-01, DP-06B</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="312" t="n">
+      <c r="H15" s="295"/>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="283" t="n">
         <v>6.0</v>
       </c>
-      <c r="B16" s="312" t="str">
+      <c r="B16" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!B15</f>
         <v>RV-06</v>
       </c>
-      <c r="C16" s="312" t="str">
+      <c r="C16" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!C15</f>
         <v>0+046.11</v>
       </c>
-      <c r="D16" s="313" t="str">
+      <c r="D16" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!D15</f>
         <v>Registro en la losa del colector; empalme cuneta Eje 06</v>
       </c>
-      <c r="E16" s="313"/>
-      <c r="F16" s="271" t="n">
+      <c r="E16" s="295"/>
+      <c r="F16" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E15</f>
         <v>1.0</v>
       </c>
-      <c r="G16" s="312" t="str">
+      <c r="G16" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F15</f>
         <v>DP-01, DP-06B</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="312" t="n">
+      <c r="H16" s="295"/>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="283" t="n">
         <v>7.0</v>
       </c>
-      <c r="B17" s="312" t="str">
+      <c r="B17" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!B16</f>
         <v>RV-07</v>
       </c>
-      <c r="C17" s="312" t="str">
+      <c r="C17" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!C16</f>
         <v>0+056.47</v>
       </c>
-      <c r="D17" s="313" t="str">
+      <c r="D17" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!D16</f>
         <v>Registro en la losa del colector; limpieza</v>
       </c>
-      <c r="E17" s="313"/>
-      <c r="F17" s="271" t="n">
+      <c r="E17" s="295"/>
+      <c r="F17" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E16</f>
         <v>1.0</v>
       </c>
-      <c r="G17" s="312" t="str">
+      <c r="G17" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F16</f>
         <v>DP-01, DP-06B</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="312" t="n">
+      <c r="H17" s="295"/>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="283" t="n">
         <v>8.0</v>
       </c>
-      <c r="B18" s="312" t="str">
+      <c r="B18" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!B17</f>
         <v>RV-08</v>
       </c>
-      <c r="C18" s="312" t="str">
+      <c r="C18" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!C17</f>
         <v>0+066.84</v>
       </c>
-      <c r="D18" s="313" t="str">
+      <c r="D18" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!D17</f>
         <v>Registro en la losa del colector; limpieza</v>
       </c>
-      <c r="E18" s="313"/>
-      <c r="F18" s="271" t="n">
+      <c r="E18" s="295"/>
+      <c r="F18" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E17</f>
         <v>1.0</v>
       </c>
-      <c r="G18" s="312" t="str">
+      <c r="G18" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F17</f>
         <v>DP-01, DP-06B</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="312" t="n">
+      <c r="H18" s="295"/>
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="283" t="n">
         <v>9.0</v>
       </c>
-      <c r="B19" s="312" t="str">
+      <c r="B19" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!B18</f>
         <v>RV-09</v>
       </c>
-      <c r="C19" s="312" t="str">
+      <c r="C19" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!C18</f>
         <v>0+077.20</v>
       </c>
-      <c r="D19" s="313" t="str">
+      <c r="D19" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!D18</f>
         <v>Registro en la losa del colector; empalme cuneta Eje 04</v>
       </c>
-      <c r="E19" s="313"/>
-      <c r="F19" s="271" t="n">
+      <c r="E19" s="295"/>
+      <c r="F19" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E18</f>
         <v>1.0</v>
       </c>
-      <c r="G19" s="312" t="str">
+      <c r="G19" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F18</f>
         <v>DP-01, DP-06B</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="312" t="n">
+      <c r="H19" s="295"/>
+    </row>
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="283" t="n">
         <v>10.0</v>
       </c>
-      <c r="B20" s="312" t="str">
+      <c r="B20" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!B19</f>
         <v>RV-10</v>
       </c>
-      <c r="C20" s="312" t="str">
+      <c r="C20" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!C19</f>
         <v>0+089.05</v>
       </c>
-      <c r="D20" s="313" t="str">
+      <c r="D20" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!D19</f>
         <v>Registro en la losa del colector; limpieza</v>
       </c>
-      <c r="E20" s="313"/>
-      <c r="F20" s="271" t="n">
+      <c r="E20" s="295"/>
+      <c r="F20" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E19</f>
         <v>1.0</v>
       </c>
-      <c r="G20" s="312" t="str">
+      <c r="G20" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F19</f>
         <v>DP-01, DP-06B</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="312" t="n">
+      <c r="H20" s="295"/>
+    </row>
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="283" t="n">
         <v>11.0</v>
       </c>
-      <c r="B21" s="312" t="str">
+      <c r="B21" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!B20</f>
         <v>RV-11</v>
       </c>
-      <c r="C21" s="312" t="str">
+      <c r="C21" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!C20</f>
         <v>0+100.90</v>
       </c>
-      <c r="D21" s="313" t="str">
+      <c r="D21" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!D20</f>
         <v>Registro en la losa del colector; quiebre; inicio del tramo de empalme con la CL</v>
       </c>
-      <c r="E21" s="313"/>
-      <c r="F21" s="271" t="n">
+      <c r="E21" s="295"/>
+      <c r="F21" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E20</f>
         <v>1.0</v>
       </c>
-      <c r="G21" s="312" t="str">
+      <c r="G21" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F20</f>
         <v>DP-01, DP-06B</v>
       </c>
+      <c r="H21" s="295"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="314"/>
-      <c r="B22" s="310" t="s">
+      <c r="A22" s="21"/>
+      <c r="B22" s="294" t="s">
         <v>1147</v>
       </c>
-      <c r="C22" s="314"/>
-      <c r="D22" s="314"/>
-      <c r="E22" s="314"/>
-      <c r="F22" s="298" t="n">
+      <c r="C22" s="295"/>
+      <c r="D22" s="295"/>
+      <c r="E22" s="295"/>
+      <c r="F22" s="296" t="n">
         <f aca="false">SUM(F11:F21)</f>
         <v>11.0</v>
       </c>
-      <c r="G22" s="314"/>
+      <c r="G22" s="295"/>
+      <c r="H22" s="295"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="310" t="s">
+      <c r="A24" s="294" t="s">
         <v>1148</v>
       </c>
-      <c r="B24" s="310"/>
-      <c r="C24" s="310"/>
-      <c r="D24" s="310"/>
-      <c r="E24" s="310"/>
-      <c r="F24" s="310"/>
-      <c r="G24" s="310"/>
-    </row>
-    <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="311" t="s">
+      <c r="B24" s="294"/>
+      <c r="C24" s="294"/>
+      <c r="D24" s="294"/>
+      <c r="E24" s="294"/>
+      <c r="F24" s="294"/>
+      <c r="G24" s="294"/>
+      <c r="H24" s="294"/>
+    </row>
+    <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="282" t="s">
         <v>309</v>
       </c>
-      <c r="B25" s="311" t="s">
+      <c r="B25" s="282" t="s">
         <v>970</v>
       </c>
-      <c r="C25" s="311" t="s">
+      <c r="C25" s="282" t="s">
         <v>170</v>
       </c>
-      <c r="D25" s="311" t="s">
+      <c r="D25" s="282" t="s">
         <v>1149</v>
       </c>
-      <c r="E25" s="311" t="s">
+      <c r="E25" s="282" t="s">
         <v>1150</v>
       </c>
-      <c r="F25" s="311" t="s">
+      <c r="F25" s="282" t="s">
         <v>169</v>
       </c>
-      <c r="G25" s="311" t="s">
+      <c r="G25" s="282" t="s">
         <v>483</v>
       </c>
+      <c r="H25" s="282"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="317"/>
-      <c r="B26" s="310" t="s">
-        <v>1151</v>
-      </c>
-      <c r="C26" s="310"/>
-      <c r="D26" s="310"/>
-      <c r="E26" s="310"/>
-      <c r="F26" s="310"/>
-      <c r="G26" s="310"/>
-    </row>
-    <row r="27" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="312" t="n">
-        <v>1</v>
-      </c>
-      <c r="B27" s="313" t="s">
-        <v>1152</v>
-      </c>
-      <c r="C27" s="315" t="s">
-        <v>50</v>
-      </c>
-      <c r="D27" s="320" t="n">
-        <f aca="false">'COLECTOR PARAMETROS'!C34*'COLECTOR PARAMETROS'!C36</f>
-        <v>5.124</v>
-      </c>
-      <c r="E27" s="302" t="n">
+      <c r="A26" s="21"/>
+      <c r="B26" s="294" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C26" s="294"/>
+      <c r="D26" s="294"/>
+      <c r="E26" s="294"/>
+      <c r="F26" s="294"/>
+      <c r="G26" s="294"/>
+      <c r="H26" s="294"/>
+    </row>
+    <row r="27" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="283" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B27" s="149" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C27" s="285" t="s">
+        <v>185</v>
+      </c>
+      <c r="D27" s="306" t="n">
+        <f aca="false">'COLECTOR PARAMETROS'!$C$31^2*'COLECTOR PARAMETROS'!$C$32</f>
+        <v>0.036992</v>
+      </c>
+      <c r="E27" s="290" t="n">
         <f aca="false">+$F$22</f>
         <v>11.0</v>
       </c>
-      <c r="F27" s="320" t="n">
+      <c r="F27" s="290" t="n">
         <f aca="false">D27*E27</f>
-        <v>56.364</v>
-      </c>
-      <c r="G27" s="313" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="312" t="n">
-        <v>2</v>
-      </c>
-      <c r="B28" s="313" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C28" s="315" t="s">
-        <v>50</v>
-      </c>
-      <c r="D28" s="320" t="n">
-        <f aca="false">'COLECTOR PARAMETROS'!C35*'COLECTOR PARAMETROS'!C37</f>
-        <v>4.9776</v>
-      </c>
-      <c r="E28" s="302" t="n">
+        <v>0.406912</v>
+      </c>
+      <c r="G27" s="149" t="s">
+        <v>1413</v>
+      </c>
+      <c r="H27" s="295"/>
+    </row>
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="21"/>
+      <c r="B28" s="294" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C28" s="285" t="s">
+        <v>185</v>
+      </c>
+      <c r="D28" s="290" t="n">
+        <f aca="false">SUM(D27:D27)</f>
+        <v>0.036992</v>
+      </c>
+      <c r="E28" s="295"/>
+      <c r="F28" s="296" t="n">
+        <f aca="false">SUM(F27:F27)</f>
+        <v>0.406912</v>
+      </c>
+      <c r="G28" s="295"/>
+      <c r="H28" s="295"/>
+    </row>
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="21"/>
+      <c r="B29" s="294" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C29" s="294"/>
+      <c r="D29" s="294"/>
+      <c r="E29" s="294"/>
+      <c r="F29" s="294"/>
+      <c r="G29" s="294"/>
+      <c r="H29" s="294"/>
+    </row>
+    <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="283" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B30" s="149" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C30" s="285" t="s">
+        <v>186</v>
+      </c>
+      <c r="D30" s="306" t="n">
+        <f aca="false">'COLECTOR PARAMETROS'!$C$35*'COLECTOR PARAMETROS'!$C$32</f>
+        <v>0.2176</v>
+      </c>
+      <c r="E30" s="290" t="n">
         <f aca="false">+$F$22</f>
         <v>11.0</v>
       </c>
-      <c r="F28" s="320" t="n">
-        <f aca="false">D28*E28</f>
-        <v>54.7536</v>
-      </c>
-      <c r="G28" s="313" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="317"/>
-      <c r="B29" s="310" t="s">
-        <v>1156</v>
-      </c>
-      <c r="C29" s="315" t="s">
+      <c r="F30" s="290" t="n">
+        <f aca="false">D30*E30</f>
+        <v>2.3936</v>
+      </c>
+      <c r="G30" s="149" t="s">
+        <v>1413</v>
+      </c>
+      <c r="H30" s="295"/>
+    </row>
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21"/>
+      <c r="B31" s="294" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C31" s="285" t="s">
+        <v>186</v>
+      </c>
+      <c r="D31" s="290" t="n">
+        <f aca="false">SUM(D30:D30)</f>
+        <v>0.2176</v>
+      </c>
+      <c r="E31" s="295"/>
+      <c r="F31" s="296" t="n">
+        <f aca="false">SUM(F30:F30)</f>
+        <v>2.3936</v>
+      </c>
+      <c r="G31" s="295"/>
+      <c r="H31" s="295"/>
+    </row>
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21"/>
+      <c r="B32" s="294" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C32" s="294"/>
+      <c r="D32" s="294"/>
+      <c r="E32" s="294"/>
+      <c r="F32" s="294"/>
+      <c r="G32" s="294"/>
+      <c r="H32" s="294"/>
+    </row>
+    <row r="33" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="283" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B33" s="149" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C33" s="285" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="323" t="n">
-        <f aca="false">SUM(D27:D28)</f>
-        <v>10.1016</v>
-      </c>
-      <c r="E29" s="314"/>
-      <c r="F29" s="298" t="n">
-        <f aca="false">SUM(F27:F28)</f>
-        <v>111.1176</v>
-      </c>
-      <c r="G29" s="314"/>
-    </row>
-    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="317"/>
-      <c r="B30" s="310" t="s">
-        <v>1157</v>
-      </c>
-      <c r="C30" s="310"/>
-      <c r="D30" s="310"/>
-      <c r="E30" s="310"/>
-      <c r="F30" s="310"/>
-      <c r="G30" s="310"/>
-    </row>
-    <row r="31" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="312" t="n">
-        <v>3</v>
-      </c>
-      <c r="B31" s="313" t="s">
-        <v>1158</v>
-      </c>
-      <c r="C31" s="315" t="s">
-        <v>185</v>
-      </c>
-      <c r="D31" s="320" t="n">
-        <f aca="false">'COLECTOR PARAMETROS'!C31*'COLECTOR PARAMETROS'!C31*'COLECTOR PARAMETROS'!C32</f>
-        <v>0.036992</v>
-      </c>
-      <c r="E31" s="302" t="n">
+      <c r="D33" s="306" t="n">
+        <f aca="false">'COLECTOR ACERO'!U18/'COLECTOR ACERO'!F18</f>
+        <v>4.8608</v>
+      </c>
+      <c r="E33" s="290" t="n">
         <f aca="false">+$F$22</f>
         <v>11.0</v>
       </c>
-      <c r="F31" s="320" t="n">
-        <f aca="false">D31*E31</f>
-        <v>0.406912</v>
-      </c>
-      <c r="G31" s="313" t="s">
-        <v>1159</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="317"/>
-      <c r="B32" s="310" t="s">
-        <v>1160</v>
-      </c>
-      <c r="C32" s="315" t="s">
-        <v>185</v>
-      </c>
-      <c r="D32" s="323" t="n">
-        <f aca="false">SUM(D31:D31)</f>
-        <v>0.036992</v>
-      </c>
-      <c r="E32" s="314"/>
-      <c r="F32" s="298" t="n">
-        <f aca="false">SUM(F31:F31)</f>
-        <v>0.406912</v>
-      </c>
-      <c r="G32" s="314"/>
-    </row>
-    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="317"/>
-      <c r="B33" s="310" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C33" s="310"/>
-      <c r="D33" s="310"/>
-      <c r="E33" s="310"/>
-      <c r="F33" s="310"/>
-      <c r="G33" s="310"/>
-    </row>
-    <row r="34" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="312" t="n">
-        <v>4</v>
-      </c>
-      <c r="B34" s="313" t="s">
-        <v>1162</v>
-      </c>
-      <c r="C34" s="315" t="s">
+      <c r="F33" s="290" t="n">
+        <f aca="false">D33*E33</f>
+        <v>53.4688</v>
+      </c>
+      <c r="G33" s="149" t="s">
+        <v>1182</v>
+      </c>
+      <c r="H33" s="295"/>
+    </row>
+    <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="283" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B34" s="149" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C34" s="285" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="320" t="n">
-        <f aca="false">'COLECTOR ACERO'!U18/'COLECTOR ACERO'!F18</f>
-        <v>4.8608</v>
-      </c>
-      <c r="E34" s="302" t="n">
+      <c r="D34" s="306" t="n">
+        <f aca="false">'COLECTOR ACERO'!U19/'COLECTOR ACERO'!F19</f>
+        <v>0.994</v>
+      </c>
+      <c r="E34" s="290" t="n">
         <f aca="false">+$F$22</f>
         <v>11.0</v>
       </c>
-      <c r="F34" s="320" t="n">
+      <c r="F34" s="290" t="n">
         <f aca="false">D34*E34</f>
-        <v>53.4688</v>
-      </c>
-      <c r="G34" s="313" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="312" t="n">
-        <v>5</v>
-      </c>
-      <c r="B35" s="313" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C35" s="315" t="s">
+        <v>10.934</v>
+      </c>
+      <c r="G34" s="149" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H34" s="295"/>
+    </row>
+    <row r="35" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="283" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B35" s="149" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C35" s="285" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="320" t="n">
-        <f aca="false">'COLECTOR ACERO'!U19/'COLECTOR ACERO'!F19</f>
-        <v>0.448</v>
-      </c>
-      <c r="E35" s="302" t="n">
+      <c r="D35" s="306" t="n">
+        <f aca="false">'COLECTOR ACERO'!U17/'COLECTOR ACERO'!F17</f>
+        <v>11.1328</v>
+      </c>
+      <c r="E35" s="290" t="n">
         <f aca="false">+$F$22</f>
         <v>11.0</v>
       </c>
-      <c r="F35" s="320" t="n">
+      <c r="F35" s="290" t="n">
         <f aca="false">D35*E35</f>
-        <v>4.928</v>
-      </c>
-      <c r="G35" s="313" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="312" t="n">
-        <v>6</v>
-      </c>
-      <c r="B36" s="313" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C36" s="315" t="s">
+        <v>122.4608</v>
+      </c>
+      <c r="G35" s="149" t="s">
+        <v>1185</v>
+      </c>
+      <c r="H35" s="295"/>
+    </row>
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21"/>
+      <c r="B36" s="294" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C36" s="285" t="s">
         <v>50</v>
       </c>
-      <c r="D36" s="320" t="n">
-        <f aca="false">'COLECTOR ACERO'!U20/'COLECTOR ACERO'!F20</f>
-        <v>0.896</v>
-      </c>
-      <c r="E36" s="302" t="n">
-        <f aca="false">+$F$22</f>
-        <v>11.0</v>
-      </c>
-      <c r="F36" s="320" t="n">
-        <f aca="false">D36*E36</f>
-        <v>9.856</v>
-      </c>
-      <c r="G36" s="313" t="s">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="312" t="n">
-        <v>7</v>
-      </c>
-      <c r="B37" s="313" t="s">
-        <v>1168</v>
-      </c>
-      <c r="C37" s="315" t="s">
+      <c r="D36" s="290" t="n">
+        <f aca="false">SUM(D33:D35)</f>
+        <v>16.9876</v>
+      </c>
+      <c r="E36" s="295"/>
+      <c r="F36" s="296" t="n">
+        <f aca="false">SUM(F33:F35)</f>
+        <v>186.8636</v>
+      </c>
+      <c r="G36" s="295"/>
+      <c r="H36" s="295"/>
+    </row>
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="294" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B38" s="294"/>
+      <c r="C38" s="294"/>
+      <c r="D38" s="294"/>
+      <c r="E38" s="294"/>
+      <c r="F38" s="294"/>
+      <c r="G38" s="294"/>
+      <c r="H38" s="294"/>
+    </row>
+    <row r="39" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="282"/>
+      <c r="B39" s="282" t="s">
+        <v>970</v>
+      </c>
+      <c r="C39" s="282" t="s">
+        <v>170</v>
+      </c>
+      <c r="D39" s="282"/>
+      <c r="E39" s="282" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F39" s="282" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G39" s="282" t="s">
+        <v>1177</v>
+      </c>
+      <c r="H39" s="282"/>
+    </row>
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="21"/>
+      <c r="B40" s="149" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C40" s="285" t="s">
+        <v>185</v>
+      </c>
+      <c r="D40" s="295"/>
+      <c r="E40" s="290" t="n">
+        <f aca="false">+F28</f>
+        <v>0.406912</v>
+      </c>
+      <c r="F40" s="290" t="n">
+        <f aca="false">'COLECTOR REGISTROS Y TAPAS'!E28</f>
+        <v>0.406912</v>
+      </c>
+      <c r="G40" s="295" t="str">
+        <f aca="false">IF(ABS(E40-F40)&lt;0.0005,"CONFORME","REVISAR")</f>
+        <v>CONFORME</v>
+      </c>
+      <c r="H40" s="295"/>
+    </row>
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="21"/>
+      <c r="B41" s="149" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C41" s="285" t="s">
+        <v>186</v>
+      </c>
+      <c r="D41" s="295"/>
+      <c r="E41" s="290" t="n">
+        <f aca="false">+F31</f>
+        <v>2.3936</v>
+      </c>
+      <c r="F41" s="290" t="n">
+        <f aca="false">'COLECTOR REGISTROS Y TAPAS'!E26</f>
+        <v>2.3936</v>
+      </c>
+      <c r="G41" s="295" t="str">
+        <f aca="false">IF(ABS(E41-F41)&lt;0.0005,"CONFORME","REVISAR")</f>
+        <v>CONFORME</v>
+      </c>
+      <c r="H41" s="295"/>
+    </row>
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="21"/>
+      <c r="B42" s="149" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C42" s="285" t="s">
         <v>50</v>
       </c>
-      <c r="D37" s="320" t="n">
-        <f aca="false">'COLECTOR ACERO'!U17/'COLECTOR ACERO'!F17</f>
-        <v>11.1328</v>
-      </c>
-      <c r="E37" s="302" t="n">
-        <f aca="false">+$F$22</f>
-        <v>11.0</v>
-      </c>
-      <c r="F37" s="320" t="n">
-        <f aca="false">D37*E37</f>
-        <v>122.4608</v>
-      </c>
-      <c r="G37" s="313" t="s">
-        <v>1185</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="317"/>
-      <c r="B38" s="310" t="s">
-        <v>1170</v>
-      </c>
-      <c r="C38" s="315" t="s">
-        <v>50</v>
-      </c>
-      <c r="D38" s="323" t="n">
-        <f aca="false">SUM(D34:D37)</f>
-        <v>17.3376</v>
-      </c>
-      <c r="E38" s="314"/>
-      <c r="F38" s="298" t="n">
-        <f aca="false">SUM(F34:F37)</f>
-        <v>190.7136</v>
-      </c>
-      <c r="G38" s="314"/>
-    </row>
-    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="317"/>
-      <c r="B39" s="310" t="s">
-        <v>1171</v>
-      </c>
-      <c r="C39" s="310"/>
-      <c r="D39" s="310"/>
-      <c r="E39" s="310"/>
-      <c r="F39" s="310"/>
-      <c r="G39" s="310"/>
-    </row>
-    <row r="40" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="312" t="n">
-        <v>8</v>
-      </c>
-      <c r="B40" s="313" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C40" s="315" t="s">
-        <v>186</v>
-      </c>
-      <c r="D40" s="320" t="n">
-        <f aca="false">'COLECTOR PARAMETROS'!C34*'COLECTOR PARAMETROS'!C38+'COLECTOR PARAMETROS'!C35*'COLECTOR PARAMETROS'!C39</f>
-        <v>0.83904</v>
-      </c>
-      <c r="E40" s="302" t="n">
-        <f aca="false">+$F$22</f>
-        <v>11.0</v>
-      </c>
-      <c r="F40" s="320" t="n">
-        <f aca="false">D40*E40</f>
-        <v>9.22944</v>
-      </c>
-      <c r="G40" s="313" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="317"/>
-      <c r="B41" s="310" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C41" s="315" t="s">
-        <v>186</v>
-      </c>
-      <c r="D41" s="323" t="n">
-        <f aca="false">SUM(D40:D40)</f>
-        <v>0.83904</v>
-      </c>
-      <c r="E41" s="314"/>
-      <c r="F41" s="298" t="n">
-        <f aca="false">SUM(F40:F40)</f>
-        <v>9.22944</v>
-      </c>
-      <c r="G41" s="314"/>
-    </row>
-    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="310" t="s">
-        <v>1174</v>
-      </c>
-      <c r="B43" s="310"/>
-      <c r="C43" s="310"/>
-      <c r="D43" s="310"/>
-      <c r="E43" s="310"/>
-      <c r="F43" s="310"/>
-      <c r="G43" s="310"/>
-    </row>
-    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="311"/>
-      <c r="B44" s="311" t="s">
-        <v>970</v>
-      </c>
-      <c r="C44" s="311" t="s">
-        <v>170</v>
-      </c>
-      <c r="D44" s="311"/>
-      <c r="E44" s="311" t="s">
-        <v>1175</v>
-      </c>
-      <c r="F44" s="311" t="s">
-        <v>1176</v>
-      </c>
-      <c r="G44" s="311" t="s">
-        <v>1177</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="317"/>
-      <c r="B45" s="313" t="s">
-        <v>1178</v>
-      </c>
-      <c r="C45" s="315" t="s">
-        <v>50</v>
-      </c>
-      <c r="D45" s="314"/>
-      <c r="E45" s="320" t="n">
-        <f aca="false">+F29</f>
-        <v>111.1176</v>
-      </c>
-      <c r="F45" s="320" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E27</f>
-        <v>111.1176</v>
-      </c>
-      <c r="G45" s="312" t="str">
-        <f aca="false">IF(ABS(E45-F45)&lt;0.001,"CONFORME","REVISAR")</f>
+      <c r="D42" s="295"/>
+      <c r="E42" s="290" t="n">
+        <f aca="false">+F36</f>
+        <v>186.8636</v>
+      </c>
+      <c r="F42" s="290" t="n">
+        <f aca="false">'COLECTOR ACERO'!U17+'COLECTOR REGISTROS Y TAPAS'!E27</f>
+        <v>186.8636</v>
+      </c>
+      <c r="G42" s="295" t="str">
+        <f aca="false">IF(ABS(E42-F42)&lt;0.0005,"CONFORME","REVISAR")</f>
         <v>CONFORME</v>
       </c>
-    </row>
-    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="317"/>
-      <c r="B46" s="313" t="s">
-        <v>1179</v>
-      </c>
-      <c r="C46" s="315" t="s">
-        <v>185</v>
-      </c>
-      <c r="D46" s="314"/>
-      <c r="E46" s="320" t="n">
-        <f aca="false">+F32</f>
-        <v>0.406912</v>
-      </c>
-      <c r="F46" s="320" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E29</f>
-        <v>0.406912</v>
-      </c>
-      <c r="G46" s="312" t="str">
-        <f aca="false">IF(ABS(E46-F46)&lt;0.001,"CONFORME","REVISAR")</f>
-        <v>CONFORME</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="317"/>
-      <c r="B47" s="313" t="s">
-        <v>1180</v>
-      </c>
-      <c r="C47" s="315" t="s">
-        <v>50</v>
-      </c>
-      <c r="D47" s="314"/>
-      <c r="E47" s="320" t="n">
-        <f aca="false">+F38</f>
-        <v>190.7136</v>
-      </c>
-      <c r="F47" s="320" t="n">
-        <f aca="false">+'COLECTOR ACERO'!I25</f>
-        <v>190.7136</v>
-      </c>
-      <c r="G47" s="312" t="str">
-        <f aca="false">IF(ABS(E47-F47)&lt;0.001,"CONFORME","REVISAR")</f>
-        <v>CONFORME</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="317"/>
-      <c r="B48" s="313" t="s">
-        <v>1181</v>
-      </c>
-      <c r="C48" s="315" t="s">
-        <v>186</v>
-      </c>
-      <c r="D48" s="314"/>
-      <c r="E48" s="320" t="n">
-        <f aca="false">+F41</f>
-        <v>9.22944</v>
-      </c>
-      <c r="F48" s="320" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E30</f>
-        <v>9.22944</v>
-      </c>
-      <c r="G48" s="312" t="str">
-        <f aca="false">IF(ABS(E48-F48)&lt;0.001,"CONFORME","REVISAR")</f>
-        <v>CONFORME</v>
-      </c>
+      <c r="H42" s="295"/>
+    </row>
+    <row r="44" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="281" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B44" s="281"/>
+      <c r="C44" s="281"/>
+      <c r="D44" s="281"/>
+      <c r="E44" s="281"/>
+      <c r="F44" s="281"/>
+      <c r="G44" s="281"/>
+      <c r="H44" s="281"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="17">
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="C2:H2"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C3:H3"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C4:H4"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="B30:G30"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B39:G39"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A44:H44"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -29138,7 +28180,7 @@
         <v>0.0011212435862069</v>
       </c>
       <c r="F40" s="271" t="n">
-        <f aca="false">'ACU TAPA REGISTRO'!F77</f>
+        <f aca="false">'ACU TAPA REGISTRO'!F43</f>
         <v>40.68</v>
       </c>
       <c r="G40" s="271" t="n">
@@ -31929,7 +30971,7 @@
         <v>0.0011212435862069</v>
       </c>
       <c r="F40" s="271" t="n">
-        <f aca="false">'ACU TAPA REGISTRO'!F77</f>
+        <f aca="false">'ACU TAPA REGISTRO'!F43</f>
         <v>40.68</v>
       </c>
       <c r="G40" s="271" t="n">
@@ -34371,7 +33413,7 @@
         <v>0.00525</v>
       </c>
       <c r="F40" s="271" t="n">
-        <f aca="false">'ACU TAPA REGISTRO'!F76</f>
+        <f aca="false">'ACU TAPA REGISTRO'!F42</f>
         <v>30.93</v>
       </c>
       <c r="G40" s="271" t="n">
@@ -34398,7 +33440,7 @@
         <v>0.000525</v>
       </c>
       <c r="F41" s="271" t="n">
-        <f aca="false">'ACU TAPA REGISTRO'!F77</f>
+        <f aca="false">'ACU TAPA REGISTRO'!F43</f>
         <v>40.68</v>
       </c>
       <c r="G41" s="271" t="n">
@@ -34425,7 +33467,7 @@
         <v>0.000135</v>
       </c>
       <c r="F42" s="271" t="n">
-        <f aca="false">'ACU TAPA REGISTRO'!F79</f>
+        <f aca="false">'ACU TAPA REGISTRO'!F45</f>
         <v>8.33</v>
       </c>
       <c r="G42" s="271" t="n">

--- a/entregables_varones/METRADO_DRENAJE_PLUVIAL_CAR_VARONES_CON_COLECTOR.xlsx
+++ b/entregables_varones/METRADO_DRENAJE_PLUVIAL_CAR_VARONES_CON_COLECTOR.xlsx
@@ -515,7 +515,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2474" uniqueCount="1423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2474" uniqueCount="1426">
   <si>
     <t xml:space="preserve">RESUMEN METRADOS DE DRENAJE PLUVIAL</t>
   </si>
@@ -4798,6 +4798,15 @@
   </si>
   <si>
     <t xml:space="preserve">No hay angulos, soldadura ni pintura: la tapa es ciega de concreto armado (lamina DP-06B rev. 02). El rebaje de asiento y el borde engrosado de la abertura se metran con el concreto de la losa del colector (hoja COLECTOR CONCRETO).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamina DP-06B rev. 02: agarre 0.15 + 2 patas de 0.02 + 2 ganchos de 0.15 (0.49, se toma 0.50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACERO DE REFUERZO fy=4200 kg/cm2 EN TAPAS, BORDES Y ASAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGISTROS DE LIMPIEZA Y TAPAS - laminas DP-06B, DD-01 y DD-02: refuerzo de borde de la abertura, parrilla de la tapa, asas de la tapa ciega (cantidad de registros de la hoja COLECTOR REGISTROS Y TAPAS)</t>
   </si>
 </sst>
 </file>
@@ -12454,7 +12463,7 @@
         <v>71</v>
       </c>
       <c r="E37" s="272" t="s">
-        <v>1346</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18716,7 +18725,7 @@
     <row r="212" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="27"/>
       <c r="B212" s="27" t="s">
-        <v>150</v>
+        <v>1424</v>
       </c>
       <c r="C212" s="28"/>
       <c r="D212" s="28"/>
@@ -19780,7 +19789,7 @@
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="296" t="s">
-        <v>697</v>
+        <v>1425</v>
       </c>
       <c r="B15" s="296"/>
       <c r="C15" s="296"/>
